--- a/reports/validation-test-report.xlsx
+++ b/reports/validation-test-report.xlsx
@@ -62,7 +62,7 @@
     <t>ASSESSMENT TIMESTAMP</t>
   </si>
   <si>
-    <t>6/8/2026, 3:54:40 pm</t>
+    <t>6/8/2026, 7:11:33 pm</t>
   </si>
   <si>
     <t>CI/CD Pipeline Security Gate</t>
@@ -3247,7 +3247,7 @@
         <v>67</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3282,7 +3282,7 @@
         <v>67</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -3317,7 +3317,7 @@
         <v>67</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -3352,7 +3352,7 @@
         <v>67</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -3387,7 +3387,7 @@
         <v>67</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -3422,7 +3422,7 @@
         <v>67</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -3457,7 +3457,7 @@
         <v>67</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -3492,7 +3492,7 @@
         <v>67</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -3527,7 +3527,7 @@
         <v>67</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -3562,7 +3562,7 @@
         <v>67</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -3597,7 +3597,7 @@
         <v>67</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -3667,7 +3667,7 @@
         <v>67</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -3702,7 +3702,7 @@
         <v>67</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>67</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -3807,7 +3807,7 @@
         <v>67</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -3842,7 +3842,7 @@
         <v>67</v>
       </c>
       <c r="K19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -3877,7 +3877,7 @@
         <v>67</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3912,7 +3912,7 @@
         <v>67</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3947,7 +3947,7 @@
         <v>67</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3982,7 +3982,7 @@
         <v>67</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -4017,7 +4017,7 @@
         <v>67</v>
       </c>
       <c r="K24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -4087,7 +4087,7 @@
         <v>67</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -4122,7 +4122,7 @@
         <v>67</v>
       </c>
       <c r="K27">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>67</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -4227,7 +4227,7 @@
         <v>67</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -4262,7 +4262,7 @@
         <v>67</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -4297,7 +4297,7 @@
         <v>67</v>
       </c>
       <c r="K32">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -4332,7 +4332,7 @@
         <v>67</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -4367,7 +4367,7 @@
         <v>67</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -4402,7 +4402,7 @@
         <v>67</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -4437,7 +4437,7 @@
         <v>67</v>
       </c>
       <c r="K36">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -4472,7 +4472,7 @@
         <v>67</v>
       </c>
       <c r="K37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -4507,7 +4507,7 @@
         <v>67</v>
       </c>
       <c r="K38">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,7 @@
         <v>67</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -4577,7 +4577,7 @@
         <v>67</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -4612,7 +4612,7 @@
         <v>67</v>
       </c>
       <c r="K41">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -4647,7 +4647,7 @@
         <v>67</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -4682,7 +4682,7 @@
         <v>67</v>
       </c>
       <c r="K43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -4717,7 +4717,7 @@
         <v>67</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -4752,7 +4752,7 @@
         <v>67</v>
       </c>
       <c r="K45">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>67</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -4822,7 +4822,7 @@
         <v>67</v>
       </c>
       <c r="K47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -4857,7 +4857,7 @@
         <v>67</v>
       </c>
       <c r="K48">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -4892,7 +4892,7 @@
         <v>67</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4927,7 +4927,7 @@
         <v>67</v>
       </c>
       <c r="K50">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4962,7 +4962,7 @@
         <v>67</v>
       </c>
       <c r="K51">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4997,7 +4997,7 @@
         <v>67</v>
       </c>
       <c r="K52">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -5067,7 +5067,7 @@
         <v>67</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>67</v>
       </c>
       <c r="K55">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -5137,7 +5137,7 @@
         <v>67</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -5172,7 +5172,7 @@
         <v>67</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -5207,7 +5207,7 @@
         <v>67</v>
       </c>
       <c r="K58">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -5242,7 +5242,7 @@
         <v>67</v>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -5277,7 +5277,7 @@
         <v>67</v>
       </c>
       <c r="K60">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -5312,7 +5312,7 @@
         <v>67</v>
       </c>
       <c r="K61">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -5347,7 +5347,7 @@
         <v>67</v>
       </c>
       <c r="K62">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -5382,7 +5382,7 @@
         <v>67</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -5417,7 +5417,7 @@
         <v>67</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -5452,7 +5452,7 @@
         <v>67</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,7 +5487,7 @@
         <v>67</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,7 +5522,7 @@
         <v>67</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,7 +5557,7 @@
         <v>67</v>
       </c>
       <c r="K68">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,7 +5592,7 @@
         <v>67</v>
       </c>
       <c r="K69">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,7 +5627,7 @@
         <v>67</v>
       </c>
       <c r="K70">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,7 +5662,7 @@
         <v>67</v>
       </c>
       <c r="K71">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,7 +5697,7 @@
         <v>67</v>
       </c>
       <c r="K72">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,7 +5732,7 @@
         <v>67</v>
       </c>
       <c r="K73">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,7 +5767,7 @@
         <v>67</v>
       </c>
       <c r="K74">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,7 +5802,7 @@
         <v>67</v>
       </c>
       <c r="K75">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,7 +5837,7 @@
         <v>67</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,7 +5872,7 @@
         <v>67</v>
       </c>
       <c r="K77">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,7 +5907,7 @@
         <v>67</v>
       </c>
       <c r="K78">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5942,7 +5942,7 @@
         <v>67</v>
       </c>
       <c r="K79">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
         <v>67</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -6012,7 +6012,7 @@
         <v>67</v>
       </c>
       <c r="K81">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -6047,7 +6047,7 @@
         <v>67</v>
       </c>
       <c r="K82">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -6152,7 +6152,7 @@
         <v>67</v>
       </c>
       <c r="K85">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -6187,7 +6187,7 @@
         <v>67</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -6292,7 +6292,7 @@
         <v>67</v>
       </c>
       <c r="K89">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -6327,7 +6327,7 @@
         <v>67</v>
       </c>
       <c r="K90">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -6362,7 +6362,7 @@
         <v>67</v>
       </c>
       <c r="K91">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -6397,7 +6397,7 @@
         <v>67</v>
       </c>
       <c r="K92">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -6432,7 +6432,7 @@
         <v>67</v>
       </c>
       <c r="K93">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -6467,7 +6467,7 @@
         <v>67</v>
       </c>
       <c r="K94">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -6502,7 +6502,7 @@
         <v>67</v>
       </c>
       <c r="K95">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -6572,7 +6572,7 @@
         <v>67</v>
       </c>
       <c r="K97">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -6607,7 +6607,7 @@
         <v>67</v>
       </c>
       <c r="K98">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -6642,7 +6642,7 @@
         <v>67</v>
       </c>
       <c r="K99">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -6712,7 +6712,7 @@
         <v>67</v>
       </c>
       <c r="K101">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -6747,7 +6747,7 @@
         <v>67</v>
       </c>
       <c r="K102">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -6782,7 +6782,7 @@
         <v>67</v>
       </c>
       <c r="K103">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -6817,7 +6817,7 @@
         <v>67</v>
       </c>
       <c r="K104">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -6852,7 +6852,7 @@
         <v>67</v>
       </c>
       <c r="K105">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -6887,7 +6887,7 @@
         <v>67</v>
       </c>
       <c r="K106">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -6922,7 +6922,7 @@
         <v>67</v>
       </c>
       <c r="K107">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6957,7 +6957,7 @@
         <v>67</v>
       </c>
       <c r="K108">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6992,7 +6992,7 @@
         <v>67</v>
       </c>
       <c r="K109">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -7027,7 +7027,7 @@
         <v>67</v>
       </c>
       <c r="K110">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -7062,7 +7062,7 @@
         <v>67</v>
       </c>
       <c r="K111">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -7097,7 +7097,7 @@
         <v>67</v>
       </c>
       <c r="K112">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -7132,7 +7132,7 @@
         <v>67</v>
       </c>
       <c r="K113">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -7202,7 +7202,7 @@
         <v>67</v>
       </c>
       <c r="K115">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -7237,7 +7237,7 @@
         <v>67</v>
       </c>
       <c r="K116">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -7272,7 +7272,7 @@
         <v>67</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -7307,7 +7307,7 @@
         <v>67</v>
       </c>
       <c r="K118">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -7342,7 +7342,7 @@
         <v>67</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -7377,7 +7377,7 @@
         <v>67</v>
       </c>
       <c r="K120">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>67</v>
       </c>
       <c r="K121">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -7447,7 +7447,7 @@
         <v>67</v>
       </c>
       <c r="K122">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -7482,7 +7482,7 @@
         <v>67</v>
       </c>
       <c r="K123">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -7517,7 +7517,7 @@
         <v>67</v>
       </c>
       <c r="K124">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -7587,7 +7587,7 @@
         <v>67</v>
       </c>
       <c r="K126">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -7622,7 +7622,7 @@
         <v>67</v>
       </c>
       <c r="K127">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -7657,7 +7657,7 @@
         <v>67</v>
       </c>
       <c r="K128">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -7692,7 +7692,7 @@
         <v>67</v>
       </c>
       <c r="K129">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -7727,7 +7727,7 @@
         <v>67</v>
       </c>
       <c r="K130">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -7797,7 +7797,7 @@
         <v>67</v>
       </c>
       <c r="K132">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -7832,7 +7832,7 @@
         <v>67</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -7902,7 +7902,7 @@
         <v>67</v>
       </c>
       <c r="K135">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -7937,7 +7937,7 @@
         <v>67</v>
       </c>
       <c r="K136">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7972,7 +7972,7 @@
         <v>67</v>
       </c>
       <c r="K137">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -8042,7 +8042,7 @@
         <v>67</v>
       </c>
       <c r="K139">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -8112,7 +8112,7 @@
         <v>67</v>
       </c>
       <c r="K141">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -8147,7 +8147,7 @@
         <v>67</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -8182,7 +8182,7 @@
         <v>67</v>
       </c>
       <c r="K143">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -8217,7 +8217,7 @@
         <v>67</v>
       </c>
       <c r="K144">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -8252,7 +8252,7 @@
         <v>67</v>
       </c>
       <c r="K145">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -8287,7 +8287,7 @@
         <v>67</v>
       </c>
       <c r="K146">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -8322,7 +8322,7 @@
         <v>67</v>
       </c>
       <c r="K147">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -8357,7 +8357,7 @@
         <v>67</v>
       </c>
       <c r="K148">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -8392,7 +8392,7 @@
         <v>67</v>
       </c>
       <c r="K149">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -8427,7 +8427,7 @@
         <v>67</v>
       </c>
       <c r="K150">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -8462,7 +8462,7 @@
         <v>67</v>
       </c>
       <c r="K151">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -8567,7 +8567,7 @@
         <v>67</v>
       </c>
       <c r="K154">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -8602,7 +8602,7 @@
         <v>67</v>
       </c>
       <c r="K155">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -8637,7 +8637,7 @@
         <v>67</v>
       </c>
       <c r="K156">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -8672,7 +8672,7 @@
         <v>67</v>
       </c>
       <c r="K157">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -8707,7 +8707,7 @@
         <v>67</v>
       </c>
       <c r="K158">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -8742,7 +8742,7 @@
         <v>67</v>
       </c>
       <c r="K159">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -8777,7 +8777,7 @@
         <v>67</v>
       </c>
       <c r="K160">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -8812,7 +8812,7 @@
         <v>67</v>
       </c>
       <c r="K161">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -8847,7 +8847,7 @@
         <v>67</v>
       </c>
       <c r="K162">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -8917,7 +8917,7 @@
         <v>67</v>
       </c>
       <c r="K164">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -8952,7 +8952,7 @@
         <v>67</v>
       </c>
       <c r="K165">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -8987,7 +8987,7 @@
         <v>67</v>
       </c>
       <c r="K166">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
         <v>67</v>
       </c>
       <c r="K167">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>67</v>
       </c>
       <c r="K168">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -9127,7 +9127,7 @@
         <v>67</v>
       </c>
       <c r="K170">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -9162,7 +9162,7 @@
         <v>67</v>
       </c>
       <c r="K171">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -9232,7 +9232,7 @@
         <v>67</v>
       </c>
       <c r="K173">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -9267,7 +9267,7 @@
         <v>67</v>
       </c>
       <c r="K174">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -9302,7 +9302,7 @@
         <v>67</v>
       </c>
       <c r="K175">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -9337,7 +9337,7 @@
         <v>67</v>
       </c>
       <c r="K176">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -9372,7 +9372,7 @@
         <v>67</v>
       </c>
       <c r="K177">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -9407,7 +9407,7 @@
         <v>67</v>
       </c>
       <c r="K178">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -9442,7 +9442,7 @@
         <v>67</v>
       </c>
       <c r="K179">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -9477,7 +9477,7 @@
         <v>67</v>
       </c>
       <c r="K180">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -9512,7 +9512,7 @@
         <v>67</v>
       </c>
       <c r="K181">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -9582,7 +9582,7 @@
         <v>67</v>
       </c>
       <c r="K183">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -9617,7 +9617,7 @@
         <v>67</v>
       </c>
       <c r="K184">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -9687,7 +9687,7 @@
         <v>67</v>
       </c>
       <c r="K186">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -9722,7 +9722,7 @@
         <v>67</v>
       </c>
       <c r="K187">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -9757,7 +9757,7 @@
         <v>67</v>
       </c>
       <c r="K188">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -9792,7 +9792,7 @@
         <v>67</v>
       </c>
       <c r="K189">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -9827,7 +9827,7 @@
         <v>67</v>
       </c>
       <c r="K190">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>67</v>
       </c>
       <c r="K191">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -9897,7 +9897,7 @@
         <v>67</v>
       </c>
       <c r="K192">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -9932,7 +9932,7 @@
         <v>67</v>
       </c>
       <c r="K193">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -9967,7 +9967,7 @@
         <v>67</v>
       </c>
       <c r="K194">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -10002,7 +10002,7 @@
         <v>67</v>
       </c>
       <c r="K195">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -10037,7 +10037,7 @@
         <v>67</v>
       </c>
       <c r="K196">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -10072,7 +10072,7 @@
         <v>67</v>
       </c>
       <c r="K197">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -10107,7 +10107,7 @@
         <v>67</v>
       </c>
       <c r="K198">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -10142,7 +10142,7 @@
         <v>67</v>
       </c>
       <c r="K199">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -10177,7 +10177,7 @@
         <v>67</v>
       </c>
       <c r="K200">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -10212,7 +10212,7 @@
         <v>67</v>
       </c>
       <c r="K201">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -10247,7 +10247,7 @@
         <v>67</v>
       </c>
       <c r="K202">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -10282,7 +10282,7 @@
         <v>67</v>
       </c>
       <c r="K203">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -10317,7 +10317,7 @@
         <v>67</v>
       </c>
       <c r="K204">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -10352,7 +10352,7 @@
         <v>67</v>
       </c>
       <c r="K205">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -10387,7 +10387,7 @@
         <v>67</v>
       </c>
       <c r="K206">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -10422,7 +10422,7 @@
         <v>67</v>
       </c>
       <c r="K207">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -10457,7 +10457,7 @@
         <v>67</v>
       </c>
       <c r="K208">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -10492,7 +10492,7 @@
         <v>67</v>
       </c>
       <c r="K209">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -10527,7 +10527,7 @@
         <v>67</v>
       </c>
       <c r="K210">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -10562,7 +10562,7 @@
         <v>67</v>
       </c>
       <c r="K211">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -10597,7 +10597,7 @@
         <v>67</v>
       </c>
       <c r="K212">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -10632,7 +10632,7 @@
         <v>67</v>
       </c>
       <c r="K213">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -10702,7 +10702,7 @@
         <v>67</v>
       </c>
       <c r="K215">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -10737,7 +10737,7 @@
         <v>67</v>
       </c>
       <c r="K216">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -10772,7 +10772,7 @@
         <v>67</v>
       </c>
       <c r="K217">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -10807,7 +10807,7 @@
         <v>67</v>
       </c>
       <c r="K218">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -10842,7 +10842,7 @@
         <v>67</v>
       </c>
       <c r="K219">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -10877,7 +10877,7 @@
         <v>67</v>
       </c>
       <c r="K220">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -10912,7 +10912,7 @@
         <v>67</v>
       </c>
       <c r="K221">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -10947,7 +10947,7 @@
         <v>67</v>
       </c>
       <c r="K222">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -10982,7 +10982,7 @@
         <v>67</v>
       </c>
       <c r="K223">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -11017,7 +11017,7 @@
         <v>67</v>
       </c>
       <c r="K224">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -11052,7 +11052,7 @@
         <v>67</v>
       </c>
       <c r="K225">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -11087,7 +11087,7 @@
         <v>67</v>
       </c>
       <c r="K226">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -11122,7 +11122,7 @@
         <v>67</v>
       </c>
       <c r="K227">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -11157,7 +11157,7 @@
         <v>67</v>
       </c>
       <c r="K228">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -11192,7 +11192,7 @@
         <v>67</v>
       </c>
       <c r="K229">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -11227,7 +11227,7 @@
         <v>67</v>
       </c>
       <c r="K230">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -11262,7 +11262,7 @@
         <v>67</v>
       </c>
       <c r="K231">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -11297,7 +11297,7 @@
         <v>67</v>
       </c>
       <c r="K232">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -11332,7 +11332,7 @@
         <v>67</v>
       </c>
       <c r="K233">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -11367,7 +11367,7 @@
         <v>67</v>
       </c>
       <c r="K234">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -11402,7 +11402,7 @@
         <v>67</v>
       </c>
       <c r="K235">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -11437,7 +11437,7 @@
         <v>67</v>
       </c>
       <c r="K236">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -11472,7 +11472,7 @@
         <v>67</v>
       </c>
       <c r="K237">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -11507,7 +11507,7 @@
         <v>67</v>
       </c>
       <c r="K238">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -11577,7 +11577,7 @@
         <v>67</v>
       </c>
       <c r="K240">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -11612,7 +11612,7 @@
         <v>67</v>
       </c>
       <c r="K241">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -11647,7 +11647,7 @@
         <v>67</v>
       </c>
       <c r="K242">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -11682,7 +11682,7 @@
         <v>67</v>
       </c>
       <c r="K243">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -11752,7 +11752,7 @@
         <v>67</v>
       </c>
       <c r="K245">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -11787,7 +11787,7 @@
         <v>67</v>
       </c>
       <c r="K246">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -11822,7 +11822,7 @@
         <v>67</v>
       </c>
       <c r="K247">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -11857,7 +11857,7 @@
         <v>67</v>
       </c>
       <c r="K248">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -11892,7 +11892,7 @@
         <v>67</v>
       </c>
       <c r="K249">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -11927,7 +11927,7 @@
         <v>67</v>
       </c>
       <c r="K250">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -11962,7 +11962,7 @@
         <v>67</v>
       </c>
       <c r="K251">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -11997,7 +11997,7 @@
         <v>67</v>
       </c>
       <c r="K252">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -12032,7 +12032,7 @@
         <v>67</v>
       </c>
       <c r="K253">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -12067,7 +12067,7 @@
         <v>67</v>
       </c>
       <c r="K254">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -12102,7 +12102,7 @@
         <v>67</v>
       </c>
       <c r="K255">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -12137,7 +12137,7 @@
         <v>67</v>
       </c>
       <c r="K256">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -12172,7 +12172,7 @@
         <v>67</v>
       </c>
       <c r="K257">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -12207,7 +12207,7 @@
         <v>67</v>
       </c>
       <c r="K258">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -12242,7 +12242,7 @@
         <v>67</v>
       </c>
       <c r="K259">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -12347,7 +12347,7 @@
         <v>67</v>
       </c>
       <c r="K262">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -12382,7 +12382,7 @@
         <v>67</v>
       </c>
       <c r="K263">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -12417,7 +12417,7 @@
         <v>67</v>
       </c>
       <c r="K264">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -12452,7 +12452,7 @@
         <v>67</v>
       </c>
       <c r="K265">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -12487,7 +12487,7 @@
         <v>67</v>
       </c>
       <c r="K266">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -12557,7 +12557,7 @@
         <v>67</v>
       </c>
       <c r="K268">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -12592,7 +12592,7 @@
         <v>67</v>
       </c>
       <c r="K269">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -12627,7 +12627,7 @@
         <v>67</v>
       </c>
       <c r="K270">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -12662,7 +12662,7 @@
         <v>67</v>
       </c>
       <c r="K271">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -12697,7 +12697,7 @@
         <v>67</v>
       </c>
       <c r="K272">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
@@ -12732,7 +12732,7 @@
         <v>67</v>
       </c>
       <c r="K273">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
@@ -12767,7 +12767,7 @@
         <v>67</v>
       </c>
       <c r="K274">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
@@ -12802,7 +12802,7 @@
         <v>67</v>
       </c>
       <c r="K275">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -12837,7 +12837,7 @@
         <v>67</v>
       </c>
       <c r="K276">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -12872,7 +12872,7 @@
         <v>67</v>
       </c>
       <c r="K277">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -12907,7 +12907,7 @@
         <v>67</v>
       </c>
       <c r="K278">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -12942,7 +12942,7 @@
         <v>67</v>
       </c>
       <c r="K279">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -12977,7 +12977,7 @@
         <v>67</v>
       </c>
       <c r="K280">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -13012,7 +13012,7 @@
         <v>67</v>
       </c>
       <c r="K281">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -13047,7 +13047,7 @@
         <v>67</v>
       </c>
       <c r="K282">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -13082,7 +13082,7 @@
         <v>67</v>
       </c>
       <c r="K283">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -13117,7 +13117,7 @@
         <v>67</v>
       </c>
       <c r="K284">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -13152,7 +13152,7 @@
         <v>67</v>
       </c>
       <c r="K285">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -13222,7 +13222,7 @@
         <v>67</v>
       </c>
       <c r="K287">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -13257,7 +13257,7 @@
         <v>67</v>
       </c>
       <c r="K288">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -13327,7 +13327,7 @@
         <v>67</v>
       </c>
       <c r="K290">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -13362,7 +13362,7 @@
         <v>67</v>
       </c>
       <c r="K291">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -13397,7 +13397,7 @@
         <v>67</v>
       </c>
       <c r="K292">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -13432,7 +13432,7 @@
         <v>67</v>
       </c>
       <c r="K293">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -13467,7 +13467,7 @@
         <v>67</v>
       </c>
       <c r="K294">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -13502,7 +13502,7 @@
         <v>67</v>
       </c>
       <c r="K295">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -13537,7 +13537,7 @@
         <v>67</v>
       </c>
       <c r="K296">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -13642,7 +13642,7 @@
         <v>67</v>
       </c>
       <c r="K299">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -13712,7 +13712,7 @@
         <v>67</v>
       </c>
       <c r="K301">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/validation-test-report.xlsx
+++ b/reports/validation-test-report.xlsx
@@ -62,7 +62,7 @@
     <t>EXECUTION TIME</t>
   </si>
   <si>
-    <t>0.01 seconds</t>
+    <t>0.02 seconds</t>
   </si>
   <si>
     <t>Automated validation engine</t>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:21:09 am</t>
+    <t>7/8/2026, 10:47:59 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.684Z</t>
+    <t>2026-08-07T05:17:59.309Z</t>
   </si>
   <si>
     <t>VAL-SEC-002</t>
@@ -188,7 +188,7 @@
     <t>email='user.name+tag@gmail.com'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.685Z</t>
+    <t>2026-08-07T05:17:59.311Z</t>
   </si>
   <si>
     <t>VAL-SEC-003</t>
@@ -248,9 +248,6 @@
     <t>Email Format Syntax &amp; RFC 5322 Rule #8</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.686Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-009</t>
   </si>
   <si>
@@ -311,6 +308,9 @@
     <t>Email Format Syntax &amp; RFC 5322 Rule #18</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.312Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-019</t>
   </si>
   <si>
@@ -434,7 +434,7 @@
     <t>Evaluated: valid=true, score=4/4, feedback='Strong'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.687Z</t>
+    <t>2026-08-07T05:17:59.313Z</t>
   </si>
   <si>
     <t>VAL-SEC-037</t>
@@ -488,9 +488,6 @@
     <t>password_sample_6 (length=18)</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.688Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-042</t>
   </si>
   <si>
@@ -545,6 +542,9 @@
     <t>password_sample_12 (length=18)</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.314Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-048</t>
   </si>
   <si>
@@ -689,9 +689,6 @@
     <t>password_sample_28 (length=18)</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.689Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-064</t>
   </si>
   <si>
@@ -776,7 +773,7 @@
     <t>Sanitizer: blocked_attack=true, sanitized_output='Goa OR 1=1'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.690Z</t>
+    <t>2026-08-07T05:17:59.316Z</t>
   </si>
   <si>
     <t>VAL-SEC-072</t>
@@ -803,9 +800,6 @@
     <t>Sanitizer: blocked_attack=true, sanitized_output='Tokyo UNION SELECT null, username, password FROM users--'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.691Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-074</t>
   </si>
   <si>
@@ -818,6 +812,9 @@
     <t>Sanitizer: blocked_attack=false, sanitized_output='Maldives'</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.317Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-075</t>
   </si>
   <si>
@@ -968,9 +965,6 @@
     <t>SQL Injection Attack Pattern Defense #26</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.692Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-097</t>
   </si>
   <si>
@@ -1136,6 +1130,9 @@
     <t>XSS Script Injection Neutralization #11</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.318Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-117</t>
   </si>
   <si>
@@ -1166,9 +1163,6 @@
     <t>XSS Script Injection Neutralization #16</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.693Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-122</t>
   </si>
   <si>
@@ -1217,6 +1211,9 @@
     <t>XSS Script Injection Neutralization #24</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.319Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-130</t>
   </si>
   <si>
@@ -1304,6 +1301,9 @@
     <t>Luhn verification: valid_card=false</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.320Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-142</t>
   </si>
   <si>
@@ -1376,9 +1376,6 @@
     <t>Payment Card Luhn Mod-10 Checksum #12</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.694Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-153</t>
   </si>
   <si>
@@ -1409,6 +1406,9 @@
     <t>Payment Card Luhn Mod-10 Checksum #17</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.321Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-158</t>
   </si>
   <si>
@@ -1517,6 +1517,9 @@
     <t>Payment Card Luhn Mod-10 Checksum #35</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.322Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-176</t>
   </si>
   <si>
@@ -1583,9 +1586,6 @@
     <t>checkIn='2026-09-07', checkOut='2026-09-10'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.695Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-182</t>
   </si>
   <si>
@@ -1766,6 +1766,9 @@
     <t>Booking Stay Date Range Rule #29</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.323Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-205</t>
   </si>
   <si>
@@ -1802,9 +1805,6 @@
     <t>Booking Stay Date Range Rule #35</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.696Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-211</t>
   </si>
   <si>
@@ -2117,9 +2117,6 @@
     <t>mime_type='image/png', file_size=3.0MB</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.697Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-243</t>
   </si>
   <si>
@@ -2262,6 +2259,9 @@
   </si>
   <si>
     <t>File Upload MIME Whitelist &amp; 15MB Size Cap #21</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:17:59.324Z</t>
   </si>
   <si>
     <t>VAL-SEC-262</t>
@@ -3446,12 +3446,12 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -3460,7 +3460,7 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -3478,12 +3478,12 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>47</v>
@@ -3492,7 +3492,7 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
@@ -3510,12 +3510,12 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
@@ -3524,7 +3524,7 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>64</v>
@@ -3542,12 +3542,12 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
@@ -3556,7 +3556,7 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>47</v>
@@ -3588,7 +3588,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
         <v>72</v>
@@ -3606,12 +3606,12 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -3620,7 +3620,7 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>75</v>
@@ -3638,12 +3638,12 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -3652,7 +3652,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>50</v>
@@ -3670,12 +3670,12 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
@@ -3684,7 +3684,7 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>57</v>
@@ -3702,12 +3702,12 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
@@ -3716,7 +3716,7 @@
         <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>61</v>
@@ -3734,12 +3734,12 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -3748,7 +3748,7 @@
         <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
         <v>64</v>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -3830,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -3862,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3894,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -3958,7 +3958,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -4054,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4086,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4118,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4214,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -4278,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -4310,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4502,12 +4502,12 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
         <v>134</v>
@@ -4516,10 +4516,10 @@
         <v>135</v>
       </c>
       <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
         <v>160</v>
-      </c>
-      <c r="E43" t="s">
-        <v>161</v>
       </c>
       <c r="F43" t="s">
         <v>138</v>
@@ -4534,12 +4534,12 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" t="s">
         <v>134</v>
@@ -4548,10 +4548,10 @@
         <v>135</v>
       </c>
       <c r="D44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" t="s">
         <v>163</v>
-      </c>
-      <c r="E44" t="s">
-        <v>164</v>
       </c>
       <c r="F44" t="s">
         <v>138</v>
@@ -4566,12 +4566,12 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" t="s">
         <v>134</v>
@@ -4580,10 +4580,10 @@
         <v>135</v>
       </c>
       <c r="D45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" t="s">
         <v>166</v>
-      </c>
-      <c r="E45" t="s">
-        <v>167</v>
       </c>
       <c r="F45" t="s">
         <v>138</v>
@@ -4598,12 +4598,12 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s">
         <v>134</v>
@@ -4612,10 +4612,10 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" t="s">
         <v>169</v>
-      </c>
-      <c r="E46" t="s">
-        <v>170</v>
       </c>
       <c r="F46" t="s">
         <v>138</v>
@@ -4630,12 +4630,12 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
         <v>134</v>
@@ -4644,10 +4644,10 @@
         <v>135</v>
       </c>
       <c r="D47" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" t="s">
         <v>172</v>
-      </c>
-      <c r="E47" t="s">
-        <v>173</v>
       </c>
       <c r="F47" t="s">
         <v>138</v>
@@ -4662,12 +4662,12 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
         <v>134</v>
@@ -4676,10 +4676,10 @@
         <v>135</v>
       </c>
       <c r="D48" t="s">
+        <v>174</v>
+      </c>
+      <c r="E48" t="s">
         <v>175</v>
-      </c>
-      <c r="E48" t="s">
-        <v>176</v>
       </c>
       <c r="F48" t="s">
         <v>138</v>
@@ -4694,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -4726,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -4790,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -4822,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -4854,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -4886,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -4918,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -4982,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5014,7 +5014,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5046,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5078,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5142,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5174,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5206,12 +5206,12 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
         <v>134</v>
@@ -5220,10 +5220,10 @@
         <v>135</v>
       </c>
       <c r="D65" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65" t="s">
         <v>227</v>
-      </c>
-      <c r="E65" t="s">
-        <v>228</v>
       </c>
       <c r="F65" t="s">
         <v>138</v>
@@ -5238,12 +5238,12 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>134</v>
@@ -5252,10 +5252,10 @@
         <v>135</v>
       </c>
       <c r="D66" t="s">
+        <v>229</v>
+      </c>
+      <c r="E66" t="s">
         <v>230</v>
-      </c>
-      <c r="E66" t="s">
-        <v>231</v>
       </c>
       <c r="F66" t="s">
         <v>138</v>
@@ -5270,12 +5270,12 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
         <v>134</v>
@@ -5284,10 +5284,10 @@
         <v>135</v>
       </c>
       <c r="D67" t="s">
+        <v>232</v>
+      </c>
+      <c r="E67" t="s">
         <v>233</v>
-      </c>
-      <c r="E67" t="s">
-        <v>234</v>
       </c>
       <c r="F67" t="s">
         <v>138</v>
@@ -5302,12 +5302,12 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
         <v>134</v>
@@ -5316,10 +5316,10 @@
         <v>135</v>
       </c>
       <c r="D68" t="s">
+        <v>235</v>
+      </c>
+      <c r="E68" t="s">
         <v>236</v>
-      </c>
-      <c r="E68" t="s">
-        <v>237</v>
       </c>
       <c r="F68" t="s">
         <v>138</v>
@@ -5334,12 +5334,12 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s">
         <v>134</v>
@@ -5348,10 +5348,10 @@
         <v>135</v>
       </c>
       <c r="D69" t="s">
+        <v>238</v>
+      </c>
+      <c r="E69" t="s">
         <v>239</v>
-      </c>
-      <c r="E69" t="s">
-        <v>240</v>
       </c>
       <c r="F69" t="s">
         <v>138</v>
@@ -5366,12 +5366,12 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s">
         <v>134</v>
@@ -5380,10 +5380,10 @@
         <v>135</v>
       </c>
       <c r="D70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E70" t="s">
         <v>242</v>
-      </c>
-      <c r="E70" t="s">
-        <v>243</v>
       </c>
       <c r="F70" t="s">
         <v>138</v>
@@ -5398,12 +5398,12 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" t="s">
         <v>134</v>
@@ -5412,10 +5412,10 @@
         <v>135</v>
       </c>
       <c r="D71" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" t="s">
         <v>245</v>
-      </c>
-      <c r="E71" t="s">
-        <v>246</v>
       </c>
       <c r="F71" t="s">
         <v>138</v>
@@ -5430,63 +5430,63 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>246</v>
+      </c>
+      <c r="B72" t="s">
         <v>247</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>248</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>249</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>250</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>251</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>252</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72" t="s">
         <v>253</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="J72" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>254</v>
+      </c>
+      <c r="B73" t="s">
+        <v>247</v>
+      </c>
+      <c r="C73" t="s">
+        <v>248</v>
+      </c>
+      <c r="D73" t="s">
         <v>255</v>
       </c>
-      <c r="B73" t="s">
-        <v>248</v>
-      </c>
-      <c r="C73" t="s">
-        <v>249</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>256</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
+        <v>251</v>
+      </c>
+      <c r="G73" t="s">
         <v>257</v>
       </c>
-      <c r="F73" t="s">
-        <v>252</v>
-      </c>
-      <c r="G73" t="s">
-        <v>258</v>
-      </c>
       <c r="H73" s="3" t="s">
         <v>53</v>
       </c>
@@ -5494,31 +5494,31 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>258</v>
+      </c>
+      <c r="B74" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74" t="s">
+        <v>248</v>
+      </c>
+      <c r="D74" t="s">
         <v>259</v>
       </c>
-      <c r="B74" t="s">
-        <v>248</v>
-      </c>
-      <c r="C74" t="s">
-        <v>249</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>260</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
+        <v>251</v>
+      </c>
+      <c r="G74" t="s">
         <v>261</v>
       </c>
-      <c r="F74" t="s">
-        <v>252</v>
-      </c>
-      <c r="G74" t="s">
-        <v>262</v>
-      </c>
       <c r="H74" s="3" t="s">
         <v>53</v>
       </c>
@@ -5526,63 +5526,63 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" t="s">
+        <v>248</v>
+      </c>
+      <c r="D75" t="s">
+        <v>263</v>
+      </c>
+      <c r="E75" t="s">
         <v>264</v>
       </c>
-      <c r="B75" t="s">
-        <v>248</v>
-      </c>
-      <c r="C75" t="s">
-        <v>249</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
+        <v>251</v>
+      </c>
+      <c r="G75" t="s">
         <v>265</v>
       </c>
-      <c r="E75" t="s">
+      <c r="H75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75" t="s">
         <v>266</v>
-      </c>
-      <c r="F75" t="s">
-        <v>252</v>
-      </c>
-      <c r="G75" t="s">
-        <v>267</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="J75" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" t="s">
+        <v>247</v>
+      </c>
+      <c r="C76" t="s">
+        <v>248</v>
+      </c>
+      <c r="D76" t="s">
         <v>268</v>
       </c>
-      <c r="B76" t="s">
-        <v>248</v>
-      </c>
-      <c r="C76" t="s">
-        <v>249</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>269</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
+        <v>251</v>
+      </c>
+      <c r="G76" t="s">
         <v>270</v>
       </c>
-      <c r="F76" t="s">
-        <v>252</v>
-      </c>
-      <c r="G76" t="s">
-        <v>271</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>53</v>
       </c>
@@ -5590,31 +5590,31 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>271</v>
+      </c>
+      <c r="B77" t="s">
+        <v>247</v>
+      </c>
+      <c r="C77" t="s">
+        <v>248</v>
+      </c>
+      <c r="D77" t="s">
         <v>272</v>
       </c>
-      <c r="B77" t="s">
-        <v>248</v>
-      </c>
-      <c r="C77" t="s">
-        <v>249</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>273</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
+        <v>251</v>
+      </c>
+      <c r="G77" t="s">
         <v>274</v>
       </c>
-      <c r="F77" t="s">
-        <v>252</v>
-      </c>
-      <c r="G77" t="s">
-        <v>275</v>
-      </c>
       <c r="H77" s="3" t="s">
         <v>53</v>
       </c>
@@ -5622,31 +5622,31 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>275</v>
+      </c>
+      <c r="B78" t="s">
+        <v>247</v>
+      </c>
+      <c r="C78" t="s">
+        <v>248</v>
+      </c>
+      <c r="D78" t="s">
         <v>276</v>
       </c>
-      <c r="B78" t="s">
-        <v>248</v>
-      </c>
-      <c r="C78" t="s">
-        <v>249</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>277</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>251</v>
+      </c>
+      <c r="G78" t="s">
         <v>278</v>
       </c>
-      <c r="F78" t="s">
-        <v>252</v>
-      </c>
-      <c r="G78" t="s">
-        <v>279</v>
-      </c>
       <c r="H78" s="3" t="s">
         <v>53</v>
       </c>
@@ -5654,31 +5654,31 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>279</v>
+      </c>
+      <c r="B79" t="s">
+        <v>247</v>
+      </c>
+      <c r="C79" t="s">
+        <v>248</v>
+      </c>
+      <c r="D79" t="s">
         <v>280</v>
       </c>
-      <c r="B79" t="s">
-        <v>248</v>
-      </c>
-      <c r="C79" t="s">
-        <v>249</v>
-      </c>
-      <c r="D79" t="s">
-        <v>281</v>
-      </c>
       <c r="E79" t="s">
+        <v>250</v>
+      </c>
+      <c r="F79" t="s">
         <v>251</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>252</v>
       </c>
-      <c r="G79" t="s">
-        <v>253</v>
-      </c>
       <c r="H79" s="3" t="s">
         <v>53</v>
       </c>
@@ -5686,31 +5686,31 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>281</v>
+      </c>
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" t="s">
         <v>282</v>
       </c>
-      <c r="B80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C80" t="s">
-        <v>249</v>
-      </c>
-      <c r="D80" t="s">
-        <v>283</v>
-      </c>
       <c r="E80" t="s">
+        <v>256</v>
+      </c>
+      <c r="F80" t="s">
+        <v>251</v>
+      </c>
+      <c r="G80" t="s">
         <v>257</v>
       </c>
-      <c r="F80" t="s">
-        <v>252</v>
-      </c>
-      <c r="G80" t="s">
-        <v>258</v>
-      </c>
       <c r="H80" s="3" t="s">
         <v>53</v>
       </c>
@@ -5718,31 +5718,31 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>283</v>
+      </c>
+      <c r="B81" t="s">
+        <v>247</v>
+      </c>
+      <c r="C81" t="s">
+        <v>248</v>
+      </c>
+      <c r="D81" t="s">
         <v>284</v>
       </c>
-      <c r="B81" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81" t="s">
-        <v>249</v>
-      </c>
-      <c r="D81" t="s">
-        <v>285</v>
-      </c>
       <c r="E81" t="s">
+        <v>260</v>
+      </c>
+      <c r="F81" t="s">
+        <v>251</v>
+      </c>
+      <c r="G81" t="s">
         <v>261</v>
       </c>
-      <c r="F81" t="s">
-        <v>252</v>
-      </c>
-      <c r="G81" t="s">
-        <v>262</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>53</v>
       </c>
@@ -5750,63 +5750,63 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>285</v>
+      </c>
+      <c r="B82" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" t="s">
         <v>286</v>
       </c>
-      <c r="B82" t="s">
-        <v>248</v>
-      </c>
-      <c r="C82" t="s">
-        <v>249</v>
-      </c>
-      <c r="D82" t="s">
-        <v>287</v>
-      </c>
       <c r="E82" t="s">
+        <v>264</v>
+      </c>
+      <c r="F82" t="s">
+        <v>251</v>
+      </c>
+      <c r="G82" t="s">
+        <v>265</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82" t="s">
         <v>266</v>
-      </c>
-      <c r="F82" t="s">
-        <v>252</v>
-      </c>
-      <c r="G82" t="s">
-        <v>267</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I82">
-        <v>1</v>
-      </c>
-      <c r="J82" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>287</v>
+      </c>
+      <c r="B83" t="s">
+        <v>247</v>
+      </c>
+      <c r="C83" t="s">
+        <v>248</v>
+      </c>
+      <c r="D83" t="s">
         <v>288</v>
       </c>
-      <c r="B83" t="s">
-        <v>248</v>
-      </c>
-      <c r="C83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D83" t="s">
-        <v>289</v>
-      </c>
       <c r="E83" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" t="s">
+        <v>251</v>
+      </c>
+      <c r="G83" t="s">
         <v>270</v>
       </c>
-      <c r="F83" t="s">
-        <v>252</v>
-      </c>
-      <c r="G83" t="s">
-        <v>271</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>53</v>
       </c>
@@ -5814,31 +5814,31 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>289</v>
+      </c>
+      <c r="B84" t="s">
+        <v>247</v>
+      </c>
+      <c r="C84" t="s">
+        <v>248</v>
+      </c>
+      <c r="D84" t="s">
         <v>290</v>
       </c>
-      <c r="B84" t="s">
-        <v>248</v>
-      </c>
-      <c r="C84" t="s">
-        <v>249</v>
-      </c>
-      <c r="D84" t="s">
-        <v>291</v>
-      </c>
       <c r="E84" t="s">
+        <v>273</v>
+      </c>
+      <c r="F84" t="s">
+        <v>251</v>
+      </c>
+      <c r="G84" t="s">
         <v>274</v>
       </c>
-      <c r="F84" t="s">
-        <v>252</v>
-      </c>
-      <c r="G84" t="s">
-        <v>275</v>
-      </c>
       <c r="H84" s="3" t="s">
         <v>53</v>
       </c>
@@ -5846,31 +5846,31 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>291</v>
+      </c>
+      <c r="B85" t="s">
+        <v>247</v>
+      </c>
+      <c r="C85" t="s">
+        <v>248</v>
+      </c>
+      <c r="D85" t="s">
         <v>292</v>
       </c>
-      <c r="B85" t="s">
-        <v>248</v>
-      </c>
-      <c r="C85" t="s">
-        <v>249</v>
-      </c>
-      <c r="D85" t="s">
-        <v>293</v>
-      </c>
       <c r="E85" t="s">
+        <v>277</v>
+      </c>
+      <c r="F85" t="s">
+        <v>251</v>
+      </c>
+      <c r="G85" t="s">
         <v>278</v>
       </c>
-      <c r="F85" t="s">
-        <v>252</v>
-      </c>
-      <c r="G85" t="s">
-        <v>279</v>
-      </c>
       <c r="H85" s="3" t="s">
         <v>53</v>
       </c>
@@ -5878,31 +5878,31 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>293</v>
+      </c>
+      <c r="B86" t="s">
+        <v>247</v>
+      </c>
+      <c r="C86" t="s">
+        <v>248</v>
+      </c>
+      <c r="D86" t="s">
         <v>294</v>
       </c>
-      <c r="B86" t="s">
-        <v>248</v>
-      </c>
-      <c r="C86" t="s">
-        <v>249</v>
-      </c>
-      <c r="D86" t="s">
-        <v>295</v>
-      </c>
       <c r="E86" t="s">
+        <v>250</v>
+      </c>
+      <c r="F86" t="s">
         <v>251</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>252</v>
       </c>
-      <c r="G86" t="s">
-        <v>253</v>
-      </c>
       <c r="H86" s="3" t="s">
         <v>53</v>
       </c>
@@ -5910,31 +5910,31 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>295</v>
+      </c>
+      <c r="B87" t="s">
+        <v>247</v>
+      </c>
+      <c r="C87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" t="s">
         <v>296</v>
       </c>
-      <c r="B87" t="s">
-        <v>248</v>
-      </c>
-      <c r="C87" t="s">
-        <v>249</v>
-      </c>
-      <c r="D87" t="s">
-        <v>297</v>
-      </c>
       <c r="E87" t="s">
+        <v>256</v>
+      </c>
+      <c r="F87" t="s">
+        <v>251</v>
+      </c>
+      <c r="G87" t="s">
         <v>257</v>
       </c>
-      <c r="F87" t="s">
-        <v>252</v>
-      </c>
-      <c r="G87" t="s">
-        <v>258</v>
-      </c>
       <c r="H87" s="3" t="s">
         <v>53</v>
       </c>
@@ -5942,31 +5942,31 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>297</v>
+      </c>
+      <c r="B88" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" t="s">
+        <v>248</v>
+      </c>
+      <c r="D88" t="s">
         <v>298</v>
       </c>
-      <c r="B88" t="s">
-        <v>248</v>
-      </c>
-      <c r="C88" t="s">
-        <v>249</v>
-      </c>
-      <c r="D88" t="s">
-        <v>299</v>
-      </c>
       <c r="E88" t="s">
+        <v>260</v>
+      </c>
+      <c r="F88" t="s">
+        <v>251</v>
+      </c>
+      <c r="G88" t="s">
         <v>261</v>
       </c>
-      <c r="F88" t="s">
-        <v>252</v>
-      </c>
-      <c r="G88" t="s">
-        <v>262</v>
-      </c>
       <c r="H88" s="3" t="s">
         <v>53</v>
       </c>
@@ -5974,63 +5974,63 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>299</v>
+      </c>
+      <c r="B89" t="s">
+        <v>247</v>
+      </c>
+      <c r="C89" t="s">
+        <v>248</v>
+      </c>
+      <c r="D89" t="s">
         <v>300</v>
       </c>
-      <c r="B89" t="s">
-        <v>248</v>
-      </c>
-      <c r="C89" t="s">
-        <v>249</v>
-      </c>
-      <c r="D89" t="s">
-        <v>301</v>
-      </c>
       <c r="E89" t="s">
+        <v>264</v>
+      </c>
+      <c r="F89" t="s">
+        <v>251</v>
+      </c>
+      <c r="G89" t="s">
+        <v>265</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
         <v>266</v>
-      </c>
-      <c r="F89" t="s">
-        <v>252</v>
-      </c>
-      <c r="G89" t="s">
-        <v>267</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I89">
-        <v>1</v>
-      </c>
-      <c r="J89" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" t="s">
+        <v>247</v>
+      </c>
+      <c r="C90" t="s">
+        <v>248</v>
+      </c>
+      <c r="D90" t="s">
         <v>302</v>
       </c>
-      <c r="B90" t="s">
-        <v>248</v>
-      </c>
-      <c r="C90" t="s">
-        <v>249</v>
-      </c>
-      <c r="D90" t="s">
-        <v>303</v>
-      </c>
       <c r="E90" t="s">
+        <v>269</v>
+      </c>
+      <c r="F90" t="s">
+        <v>251</v>
+      </c>
+      <c r="G90" t="s">
         <v>270</v>
       </c>
-      <c r="F90" t="s">
-        <v>252</v>
-      </c>
-      <c r="G90" t="s">
-        <v>271</v>
-      </c>
       <c r="H90" s="3" t="s">
         <v>53</v>
       </c>
@@ -6038,31 +6038,31 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>303</v>
+      </c>
+      <c r="B91" t="s">
+        <v>247</v>
+      </c>
+      <c r="C91" t="s">
+        <v>248</v>
+      </c>
+      <c r="D91" t="s">
         <v>304</v>
       </c>
-      <c r="B91" t="s">
-        <v>248</v>
-      </c>
-      <c r="C91" t="s">
-        <v>249</v>
-      </c>
-      <c r="D91" t="s">
-        <v>305</v>
-      </c>
       <c r="E91" t="s">
+        <v>273</v>
+      </c>
+      <c r="F91" t="s">
+        <v>251</v>
+      </c>
+      <c r="G91" t="s">
         <v>274</v>
       </c>
-      <c r="F91" t="s">
-        <v>252</v>
-      </c>
-      <c r="G91" t="s">
-        <v>275</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>53</v>
       </c>
@@ -6070,31 +6070,31 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>305</v>
+      </c>
+      <c r="B92" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" t="s">
+        <v>248</v>
+      </c>
+      <c r="D92" t="s">
         <v>306</v>
       </c>
-      <c r="B92" t="s">
-        <v>248</v>
-      </c>
-      <c r="C92" t="s">
-        <v>249</v>
-      </c>
-      <c r="D92" t="s">
-        <v>307</v>
-      </c>
       <c r="E92" t="s">
+        <v>277</v>
+      </c>
+      <c r="F92" t="s">
+        <v>251</v>
+      </c>
+      <c r="G92" t="s">
         <v>278</v>
       </c>
-      <c r="F92" t="s">
-        <v>252</v>
-      </c>
-      <c r="G92" t="s">
-        <v>279</v>
-      </c>
       <c r="H92" s="3" t="s">
         <v>53</v>
       </c>
@@ -6102,31 +6102,31 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>307</v>
+      </c>
+      <c r="B93" t="s">
+        <v>247</v>
+      </c>
+      <c r="C93" t="s">
+        <v>248</v>
+      </c>
+      <c r="D93" t="s">
         <v>308</v>
       </c>
-      <c r="B93" t="s">
-        <v>248</v>
-      </c>
-      <c r="C93" t="s">
-        <v>249</v>
-      </c>
-      <c r="D93" t="s">
-        <v>309</v>
-      </c>
       <c r="E93" t="s">
+        <v>250</v>
+      </c>
+      <c r="F93" t="s">
         <v>251</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>252</v>
       </c>
-      <c r="G93" t="s">
-        <v>253</v>
-      </c>
       <c r="H93" s="3" t="s">
         <v>53</v>
       </c>
@@ -6134,31 +6134,31 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>309</v>
+      </c>
+      <c r="B94" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" t="s">
+        <v>248</v>
+      </c>
+      <c r="D94" t="s">
         <v>310</v>
       </c>
-      <c r="B94" t="s">
-        <v>248</v>
-      </c>
-      <c r="C94" t="s">
-        <v>249</v>
-      </c>
-      <c r="D94" t="s">
-        <v>311</v>
-      </c>
       <c r="E94" t="s">
+        <v>256</v>
+      </c>
+      <c r="F94" t="s">
+        <v>251</v>
+      </c>
+      <c r="G94" t="s">
         <v>257</v>
       </c>
-      <c r="F94" t="s">
-        <v>252</v>
-      </c>
-      <c r="G94" t="s">
-        <v>258</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>53</v>
       </c>
@@ -6166,31 +6166,31 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>311</v>
+      </c>
+      <c r="B95" t="s">
+        <v>247</v>
+      </c>
+      <c r="C95" t="s">
+        <v>248</v>
+      </c>
+      <c r="D95" t="s">
         <v>312</v>
       </c>
-      <c r="B95" t="s">
-        <v>248</v>
-      </c>
-      <c r="C95" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" t="s">
-        <v>313</v>
-      </c>
       <c r="E95" t="s">
+        <v>260</v>
+      </c>
+      <c r="F95" t="s">
+        <v>251</v>
+      </c>
+      <c r="G95" t="s">
         <v>261</v>
       </c>
-      <c r="F95" t="s">
-        <v>252</v>
-      </c>
-      <c r="G95" t="s">
-        <v>262</v>
-      </c>
       <c r="H95" s="3" t="s">
         <v>53</v>
       </c>
@@ -6198,63 +6198,63 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>313</v>
+      </c>
+      <c r="B96" t="s">
+        <v>247</v>
+      </c>
+      <c r="C96" t="s">
+        <v>248</v>
+      </c>
+      <c r="D96" t="s">
         <v>314</v>
       </c>
-      <c r="B96" t="s">
-        <v>248</v>
-      </c>
-      <c r="C96" t="s">
-        <v>249</v>
-      </c>
-      <c r="D96" t="s">
-        <v>315</v>
-      </c>
       <c r="E96" t="s">
+        <v>264</v>
+      </c>
+      <c r="F96" t="s">
+        <v>251</v>
+      </c>
+      <c r="G96" t="s">
+        <v>265</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
         <v>266</v>
-      </c>
-      <c r="F96" t="s">
-        <v>252</v>
-      </c>
-      <c r="G96" t="s">
-        <v>267</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>315</v>
+      </c>
+      <c r="B97" t="s">
+        <v>247</v>
+      </c>
+      <c r="C97" t="s">
+        <v>248</v>
+      </c>
+      <c r="D97" t="s">
         <v>316</v>
       </c>
-      <c r="B97" t="s">
-        <v>248</v>
-      </c>
-      <c r="C97" t="s">
-        <v>249</v>
-      </c>
-      <c r="D97" t="s">
-        <v>317</v>
-      </c>
       <c r="E97" t="s">
+        <v>269</v>
+      </c>
+      <c r="F97" t="s">
+        <v>251</v>
+      </c>
+      <c r="G97" t="s">
         <v>270</v>
       </c>
-      <c r="F97" t="s">
-        <v>252</v>
-      </c>
-      <c r="G97" t="s">
-        <v>271</v>
-      </c>
       <c r="H97" s="3" t="s">
         <v>53</v>
       </c>
@@ -6262,31 +6262,31 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B98" t="s">
+        <v>247</v>
+      </c>
+      <c r="C98" t="s">
         <v>248</v>
       </c>
-      <c r="C98" t="s">
-        <v>249</v>
-      </c>
       <c r="D98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E98" t="s">
+        <v>273</v>
+      </c>
+      <c r="F98" t="s">
+        <v>251</v>
+      </c>
+      <c r="G98" t="s">
         <v>274</v>
       </c>
-      <c r="F98" t="s">
-        <v>252</v>
-      </c>
-      <c r="G98" t="s">
-        <v>275</v>
-      </c>
       <c r="H98" s="3" t="s">
         <v>53</v>
       </c>
@@ -6294,31 +6294,31 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B99" t="s">
+        <v>247</v>
+      </c>
+      <c r="C99" t="s">
         <v>248</v>
       </c>
-      <c r="C99" t="s">
-        <v>249</v>
-      </c>
       <c r="D99" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E99" t="s">
+        <v>277</v>
+      </c>
+      <c r="F99" t="s">
+        <v>251</v>
+      </c>
+      <c r="G99" t="s">
         <v>278</v>
       </c>
-      <c r="F99" t="s">
-        <v>252</v>
-      </c>
-      <c r="G99" t="s">
-        <v>279</v>
-      </c>
       <c r="H99" s="3" t="s">
         <v>53</v>
       </c>
@@ -6326,31 +6326,31 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B100" t="s">
+        <v>247</v>
+      </c>
+      <c r="C100" t="s">
         <v>248</v>
       </c>
-      <c r="C100" t="s">
-        <v>249</v>
-      </c>
       <c r="D100" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E100" t="s">
+        <v>250</v>
+      </c>
+      <c r="F100" t="s">
         <v>251</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>252</v>
       </c>
-      <c r="G100" t="s">
-        <v>253</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>53</v>
       </c>
@@ -6358,31 +6358,31 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B101" t="s">
+        <v>247</v>
+      </c>
+      <c r="C101" t="s">
         <v>248</v>
       </c>
-      <c r="C101" t="s">
-        <v>249</v>
-      </c>
       <c r="D101" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E101" t="s">
+        <v>256</v>
+      </c>
+      <c r="F101" t="s">
+        <v>251</v>
+      </c>
+      <c r="G101" t="s">
         <v>257</v>
       </c>
-      <c r="F101" t="s">
-        <v>252</v>
-      </c>
-      <c r="G101" t="s">
-        <v>258</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>53</v>
       </c>
@@ -6390,31 +6390,31 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B102" t="s">
+        <v>247</v>
+      </c>
+      <c r="C102" t="s">
         <v>248</v>
       </c>
-      <c r="C102" t="s">
-        <v>249</v>
-      </c>
       <c r="D102" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E102" t="s">
+        <v>260</v>
+      </c>
+      <c r="F102" t="s">
+        <v>251</v>
+      </c>
+      <c r="G102" t="s">
         <v>261</v>
       </c>
-      <c r="F102" t="s">
-        <v>252</v>
-      </c>
-      <c r="G102" t="s">
-        <v>262</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>53</v>
       </c>
@@ -6422,63 +6422,63 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B103" t="s">
+        <v>247</v>
+      </c>
+      <c r="C103" t="s">
         <v>248</v>
       </c>
-      <c r="C103" t="s">
-        <v>249</v>
-      </c>
       <c r="D103" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E103" t="s">
+        <v>264</v>
+      </c>
+      <c r="F103" t="s">
+        <v>251</v>
+      </c>
+      <c r="G103" t="s">
+        <v>265</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103" t="s">
         <v>266</v>
-      </c>
-      <c r="F103" t="s">
-        <v>252</v>
-      </c>
-      <c r="G103" t="s">
-        <v>267</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I103">
-        <v>1</v>
-      </c>
-      <c r="J103" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B104" t="s">
+        <v>247</v>
+      </c>
+      <c r="C104" t="s">
         <v>248</v>
       </c>
-      <c r="C104" t="s">
-        <v>249</v>
-      </c>
       <c r="D104" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E104" t="s">
+        <v>269</v>
+      </c>
+      <c r="F104" t="s">
+        <v>251</v>
+      </c>
+      <c r="G104" t="s">
         <v>270</v>
       </c>
-      <c r="F104" t="s">
-        <v>252</v>
-      </c>
-      <c r="G104" t="s">
-        <v>271</v>
-      </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
       </c>
@@ -6486,31 +6486,31 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s">
+        <v>247</v>
+      </c>
+      <c r="C105" t="s">
         <v>248</v>
       </c>
-      <c r="C105" t="s">
-        <v>249</v>
-      </c>
       <c r="D105" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E105" t="s">
+        <v>273</v>
+      </c>
+      <c r="F105" t="s">
+        <v>251</v>
+      </c>
+      <c r="G105" t="s">
         <v>274</v>
       </c>
-      <c r="F105" t="s">
-        <v>252</v>
-      </c>
-      <c r="G105" t="s">
-        <v>275</v>
-      </c>
       <c r="H105" s="3" t="s">
         <v>53</v>
       </c>
@@ -6518,31 +6518,31 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s">
+        <v>247</v>
+      </c>
+      <c r="C106" t="s">
         <v>248</v>
       </c>
-      <c r="C106" t="s">
-        <v>249</v>
-      </c>
       <c r="D106" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E106" t="s">
+        <v>277</v>
+      </c>
+      <c r="F106" t="s">
+        <v>251</v>
+      </c>
+      <c r="G106" t="s">
         <v>278</v>
       </c>
-      <c r="F106" t="s">
-        <v>252</v>
-      </c>
-      <c r="G106" t="s">
-        <v>279</v>
-      </c>
       <c r="H106" s="3" t="s">
         <v>53</v>
       </c>
@@ -6550,31 +6550,31 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>335</v>
+      </c>
+      <c r="B107" t="s">
+        <v>336</v>
+      </c>
+      <c r="C107" t="s">
         <v>337</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
         <v>338</v>
       </c>
-      <c r="C107" t="s">
+      <c r="E107" t="s">
         <v>339</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>340</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>341</v>
       </c>
-      <c r="F107" t="s">
-        <v>342</v>
-      </c>
-      <c r="G107" t="s">
-        <v>343</v>
-      </c>
       <c r="H107" s="3" t="s">
         <v>53</v>
       </c>
@@ -6582,31 +6582,31 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>342</v>
+      </c>
+      <c r="B108" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108" t="s">
+        <v>337</v>
+      </c>
+      <c r="D108" t="s">
+        <v>343</v>
+      </c>
+      <c r="E108" t="s">
         <v>344</v>
       </c>
-      <c r="B108" t="s">
-        <v>338</v>
-      </c>
-      <c r="C108" t="s">
-        <v>339</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
+        <v>340</v>
+      </c>
+      <c r="G108" t="s">
         <v>345</v>
       </c>
-      <c r="E108" t="s">
-        <v>346</v>
-      </c>
-      <c r="F108" t="s">
-        <v>342</v>
-      </c>
-      <c r="G108" t="s">
-        <v>347</v>
-      </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
       </c>
@@ -6614,31 +6614,31 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>346</v>
+      </c>
+      <c r="B109" t="s">
+        <v>336</v>
+      </c>
+      <c r="C109" t="s">
+        <v>337</v>
+      </c>
+      <c r="D109" t="s">
+        <v>347</v>
+      </c>
+      <c r="E109" t="s">
         <v>348</v>
       </c>
-      <c r="B109" t="s">
-        <v>338</v>
-      </c>
-      <c r="C109" t="s">
-        <v>339</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
+        <v>340</v>
+      </c>
+      <c r="G109" t="s">
         <v>349</v>
       </c>
-      <c r="E109" t="s">
-        <v>350</v>
-      </c>
-      <c r="F109" t="s">
-        <v>342</v>
-      </c>
-      <c r="G109" t="s">
-        <v>351</v>
-      </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
       </c>
@@ -6646,31 +6646,31 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>350</v>
+      </c>
+      <c r="B110" t="s">
+        <v>336</v>
+      </c>
+      <c r="C110" t="s">
+        <v>337</v>
+      </c>
+      <c r="D110" t="s">
+        <v>351</v>
+      </c>
+      <c r="E110" t="s">
         <v>352</v>
       </c>
-      <c r="B110" t="s">
-        <v>338</v>
-      </c>
-      <c r="C110" t="s">
-        <v>339</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
+        <v>340</v>
+      </c>
+      <c r="G110" t="s">
         <v>353</v>
       </c>
-      <c r="E110" t="s">
-        <v>354</v>
-      </c>
-      <c r="F110" t="s">
-        <v>342</v>
-      </c>
-      <c r="G110" t="s">
-        <v>355</v>
-      </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
       </c>
@@ -6678,31 +6678,31 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>354</v>
+      </c>
+      <c r="B111" t="s">
+        <v>336</v>
+      </c>
+      <c r="C111" t="s">
+        <v>337</v>
+      </c>
+      <c r="D111" t="s">
+        <v>355</v>
+      </c>
+      <c r="E111" t="s">
         <v>356</v>
       </c>
-      <c r="B111" t="s">
-        <v>338</v>
-      </c>
-      <c r="C111" t="s">
-        <v>339</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
+        <v>340</v>
+      </c>
+      <c r="G111" t="s">
         <v>357</v>
       </c>
-      <c r="E111" t="s">
-        <v>358</v>
-      </c>
-      <c r="F111" t="s">
-        <v>342</v>
-      </c>
-      <c r="G111" t="s">
-        <v>359</v>
-      </c>
       <c r="H111" s="3" t="s">
         <v>53</v>
       </c>
@@ -6710,31 +6710,31 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>358</v>
+      </c>
+      <c r="B112" t="s">
+        <v>336</v>
+      </c>
+      <c r="C112" t="s">
+        <v>337</v>
+      </c>
+      <c r="D112" t="s">
+        <v>359</v>
+      </c>
+      <c r="E112" t="s">
         <v>360</v>
       </c>
-      <c r="B112" t="s">
-        <v>338</v>
-      </c>
-      <c r="C112" t="s">
-        <v>339</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
+        <v>340</v>
+      </c>
+      <c r="G112" t="s">
         <v>361</v>
       </c>
-      <c r="E112" t="s">
-        <v>362</v>
-      </c>
-      <c r="F112" t="s">
-        <v>342</v>
-      </c>
-      <c r="G112" t="s">
-        <v>363</v>
-      </c>
       <c r="H112" s="3" t="s">
         <v>53</v>
       </c>
@@ -6742,31 +6742,31 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B113" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C113" t="s">
+        <v>337</v>
+      </c>
+      <c r="D113" t="s">
+        <v>363</v>
+      </c>
+      <c r="E113" t="s">
         <v>339</v>
       </c>
-      <c r="D113" t="s">
-        <v>365</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>340</v>
+      </c>
+      <c r="G113" t="s">
         <v>341</v>
       </c>
-      <c r="F113" t="s">
-        <v>342</v>
-      </c>
-      <c r="G113" t="s">
-        <v>343</v>
-      </c>
       <c r="H113" s="3" t="s">
         <v>53</v>
       </c>
@@ -6774,30 +6774,30 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B114" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C114" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E114" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F114" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G114" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>53</v>
@@ -6806,30 +6806,30 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B115" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C115" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E115" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F115" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G115" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>53</v>
@@ -6838,30 +6838,30 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E116" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F116" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G116" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>53</v>
@@ -6870,62 +6870,62 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>370</v>
+      </c>
+      <c r="B117" t="s">
+        <v>336</v>
+      </c>
+      <c r="C117" t="s">
+        <v>337</v>
+      </c>
+      <c r="D117" t="s">
+        <v>371</v>
+      </c>
+      <c r="E117" t="s">
+        <v>356</v>
+      </c>
+      <c r="F117" t="s">
+        <v>340</v>
+      </c>
+      <c r="G117" t="s">
+        <v>357</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
         <v>372</v>
-      </c>
-      <c r="B117" t="s">
-        <v>338</v>
-      </c>
-      <c r="C117" t="s">
-        <v>339</v>
-      </c>
-      <c r="D117" t="s">
-        <v>373</v>
-      </c>
-      <c r="E117" t="s">
-        <v>358</v>
-      </c>
-      <c r="F117" t="s">
-        <v>342</v>
-      </c>
-      <c r="G117" t="s">
-        <v>359</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>373</v>
+      </c>
+      <c r="B118" t="s">
+        <v>336</v>
+      </c>
+      <c r="C118" t="s">
+        <v>337</v>
+      </c>
+      <c r="D118" t="s">
         <v>374</v>
       </c>
-      <c r="B118" t="s">
-        <v>338</v>
-      </c>
-      <c r="C118" t="s">
-        <v>339</v>
-      </c>
-      <c r="D118" t="s">
-        <v>375</v>
-      </c>
       <c r="E118" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G118" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>53</v>
@@ -6934,31 +6934,31 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>375</v>
+      </c>
+      <c r="B119" t="s">
+        <v>336</v>
+      </c>
+      <c r="C119" t="s">
+        <v>337</v>
+      </c>
+      <c r="D119" t="s">
         <v>376</v>
       </c>
-      <c r="B119" t="s">
-        <v>338</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="E119" t="s">
         <v>339</v>
       </c>
-      <c r="D119" t="s">
-        <v>377</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
+        <v>340</v>
+      </c>
+      <c r="G119" t="s">
         <v>341</v>
       </c>
-      <c r="F119" t="s">
-        <v>342</v>
-      </c>
-      <c r="G119" t="s">
-        <v>343</v>
-      </c>
       <c r="H119" s="3" t="s">
         <v>53</v>
       </c>
@@ -6966,30 +6966,30 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>377</v>
+      </c>
+      <c r="B120" t="s">
+        <v>336</v>
+      </c>
+      <c r="C120" t="s">
+        <v>337</v>
+      </c>
+      <c r="D120" t="s">
         <v>378</v>
       </c>
-      <c r="B120" t="s">
-        <v>338</v>
-      </c>
-      <c r="C120" t="s">
-        <v>339</v>
-      </c>
-      <c r="D120" t="s">
-        <v>379</v>
-      </c>
       <c r="E120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F120" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>53</v>
@@ -6998,30 +6998,30 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>379</v>
+      </c>
+      <c r="B121" t="s">
+        <v>336</v>
+      </c>
+      <c r="C121" t="s">
+        <v>337</v>
+      </c>
+      <c r="D121" t="s">
         <v>380</v>
       </c>
-      <c r="B121" t="s">
-        <v>338</v>
-      </c>
-      <c r="C121" t="s">
-        <v>339</v>
-      </c>
-      <c r="D121" t="s">
-        <v>381</v>
-      </c>
       <c r="E121" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F121" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G121" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>53</v>
@@ -7030,30 +7030,30 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>381</v>
+      </c>
+      <c r="B122" t="s">
+        <v>336</v>
+      </c>
+      <c r="C122" t="s">
+        <v>337</v>
+      </c>
+      <c r="D122" t="s">
         <v>382</v>
       </c>
-      <c r="B122" t="s">
-        <v>338</v>
-      </c>
-      <c r="C122" t="s">
-        <v>339</v>
-      </c>
-      <c r="D122" t="s">
-        <v>383</v>
-      </c>
       <c r="E122" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F122" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G122" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>53</v>
@@ -7062,30 +7062,30 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C123" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E123" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F123" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G123" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>53</v>
@@ -7094,30 +7094,30 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B124" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C124" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E124" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F124" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G124" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
@@ -7126,31 +7126,31 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B125" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C125" t="s">
+        <v>337</v>
+      </c>
+      <c r="D125" t="s">
+        <v>388</v>
+      </c>
+      <c r="E125" t="s">
         <v>339</v>
       </c>
-      <c r="D125" t="s">
-        <v>390</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
+        <v>340</v>
+      </c>
+      <c r="G125" t="s">
         <v>341</v>
       </c>
-      <c r="F125" t="s">
-        <v>342</v>
-      </c>
-      <c r="G125" t="s">
-        <v>343</v>
-      </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
       </c>
@@ -7158,30 +7158,30 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B126" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C126" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D126" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E126" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F126" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G126" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
@@ -7190,30 +7190,30 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B127" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C127" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E127" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F127" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G127" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
@@ -7222,30 +7222,30 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B128" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C128" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E128" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F128" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G128" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
@@ -7254,30 +7254,30 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B129" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C129" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D129" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E129" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F129" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G129" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
@@ -7286,63 +7286,63 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>397</v>
+      </c>
+      <c r="B130" t="s">
+        <v>336</v>
+      </c>
+      <c r="C130" t="s">
+        <v>337</v>
+      </c>
+      <c r="D130" t="s">
+        <v>398</v>
+      </c>
+      <c r="E130" t="s">
+        <v>360</v>
+      </c>
+      <c r="F130" t="s">
+        <v>340</v>
+      </c>
+      <c r="G130" t="s">
+        <v>361</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130" t="s">
         <v>399</v>
-      </c>
-      <c r="B130" t="s">
-        <v>338</v>
-      </c>
-      <c r="C130" t="s">
-        <v>339</v>
-      </c>
-      <c r="D130" t="s">
-        <v>400</v>
-      </c>
-      <c r="E130" t="s">
-        <v>362</v>
-      </c>
-      <c r="F130" t="s">
-        <v>342</v>
-      </c>
-      <c r="G130" t="s">
-        <v>363</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I130">
-        <v>1</v>
-      </c>
-      <c r="J130" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>400</v>
+      </c>
+      <c r="B131" t="s">
+        <v>336</v>
+      </c>
+      <c r="C131" t="s">
+        <v>337</v>
+      </c>
+      <c r="D131" t="s">
         <v>401</v>
       </c>
-      <c r="B131" t="s">
-        <v>338</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="E131" t="s">
         <v>339</v>
       </c>
-      <c r="D131" t="s">
-        <v>402</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G131" t="s">
         <v>341</v>
       </c>
-      <c r="F131" t="s">
-        <v>342</v>
-      </c>
-      <c r="G131" t="s">
-        <v>343</v>
-      </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
       </c>
@@ -7350,30 +7350,30 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>402</v>
+      </c>
+      <c r="B132" t="s">
+        <v>336</v>
+      </c>
+      <c r="C132" t="s">
+        <v>337</v>
+      </c>
+      <c r="D132" t="s">
         <v>403</v>
       </c>
-      <c r="B132" t="s">
-        <v>338</v>
-      </c>
-      <c r="C132" t="s">
-        <v>339</v>
-      </c>
-      <c r="D132" t="s">
-        <v>404</v>
-      </c>
       <c r="E132" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F132" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G132" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
@@ -7382,30 +7382,30 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>404</v>
+      </c>
+      <c r="B133" t="s">
+        <v>336</v>
+      </c>
+      <c r="C133" t="s">
+        <v>337</v>
+      </c>
+      <c r="D133" t="s">
         <v>405</v>
       </c>
-      <c r="B133" t="s">
-        <v>338</v>
-      </c>
-      <c r="C133" t="s">
-        <v>339</v>
-      </c>
-      <c r="D133" t="s">
-        <v>406</v>
-      </c>
       <c r="E133" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F133" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G133" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
@@ -7414,30 +7414,30 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>406</v>
+      </c>
+      <c r="B134" t="s">
+        <v>336</v>
+      </c>
+      <c r="C134" t="s">
+        <v>337</v>
+      </c>
+      <c r="D134" t="s">
         <v>407</v>
       </c>
-      <c r="B134" t="s">
-        <v>338</v>
-      </c>
-      <c r="C134" t="s">
-        <v>339</v>
-      </c>
-      <c r="D134" t="s">
-        <v>408</v>
-      </c>
       <c r="E134" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F134" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G134" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
@@ -7446,30 +7446,30 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>408</v>
+      </c>
+      <c r="B135" t="s">
+        <v>336</v>
+      </c>
+      <c r="C135" t="s">
+        <v>337</v>
+      </c>
+      <c r="D135" t="s">
         <v>409</v>
       </c>
-      <c r="B135" t="s">
-        <v>338</v>
-      </c>
-      <c r="C135" t="s">
-        <v>339</v>
-      </c>
-      <c r="D135" t="s">
-        <v>410</v>
-      </c>
       <c r="E135" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F135" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G135" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
@@ -7478,30 +7478,30 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>410</v>
+      </c>
+      <c r="B136" t="s">
+        <v>336</v>
+      </c>
+      <c r="C136" t="s">
+        <v>337</v>
+      </c>
+      <c r="D136" t="s">
         <v>411</v>
       </c>
-      <c r="B136" t="s">
-        <v>338</v>
-      </c>
-      <c r="C136" t="s">
-        <v>339</v>
-      </c>
-      <c r="D136" t="s">
-        <v>412</v>
-      </c>
       <c r="E136" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F136" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G136" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
@@ -7510,31 +7510,31 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>412</v>
+      </c>
+      <c r="B137" t="s">
+        <v>336</v>
+      </c>
+      <c r="C137" t="s">
+        <v>337</v>
+      </c>
+      <c r="D137" t="s">
         <v>413</v>
       </c>
-      <c r="B137" t="s">
-        <v>338</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="E137" t="s">
         <v>339</v>
       </c>
-      <c r="D137" t="s">
-        <v>414</v>
-      </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
+        <v>340</v>
+      </c>
+      <c r="G137" t="s">
         <v>341</v>
       </c>
-      <c r="F137" t="s">
-        <v>342</v>
-      </c>
-      <c r="G137" t="s">
-        <v>343</v>
-      </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
       </c>
@@ -7542,30 +7542,30 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>414</v>
+      </c>
+      <c r="B138" t="s">
+        <v>336</v>
+      </c>
+      <c r="C138" t="s">
+        <v>337</v>
+      </c>
+      <c r="D138" t="s">
         <v>415</v>
       </c>
-      <c r="B138" t="s">
-        <v>338</v>
-      </c>
-      <c r="C138" t="s">
-        <v>339</v>
-      </c>
-      <c r="D138" t="s">
-        <v>416</v>
-      </c>
       <c r="E138" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F138" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G138" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
@@ -7574,30 +7574,30 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>416</v>
+      </c>
+      <c r="B139" t="s">
+        <v>336</v>
+      </c>
+      <c r="C139" t="s">
+        <v>337</v>
+      </c>
+      <c r="D139" t="s">
         <v>417</v>
       </c>
-      <c r="B139" t="s">
-        <v>338</v>
-      </c>
-      <c r="C139" t="s">
-        <v>339</v>
-      </c>
-      <c r="D139" t="s">
-        <v>418</v>
-      </c>
       <c r="E139" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F139" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G139" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>53</v>
@@ -7606,30 +7606,30 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>418</v>
+      </c>
+      <c r="B140" t="s">
+        <v>336</v>
+      </c>
+      <c r="C140" t="s">
+        <v>337</v>
+      </c>
+      <c r="D140" t="s">
         <v>419</v>
       </c>
-      <c r="B140" t="s">
-        <v>338</v>
-      </c>
-      <c r="C140" t="s">
-        <v>339</v>
-      </c>
-      <c r="D140" t="s">
-        <v>420</v>
-      </c>
       <c r="E140" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F140" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G140" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>53</v>
@@ -7638,30 +7638,30 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>420</v>
+      </c>
+      <c r="B141" t="s">
+        <v>336</v>
+      </c>
+      <c r="C141" t="s">
+        <v>337</v>
+      </c>
+      <c r="D141" t="s">
         <v>421</v>
       </c>
-      <c r="B141" t="s">
-        <v>338</v>
-      </c>
-      <c r="C141" t="s">
-        <v>339</v>
-      </c>
-      <c r="D141" t="s">
-        <v>422</v>
-      </c>
       <c r="E141" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F141" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G141" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>53</v>
@@ -7670,39 +7670,39 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>422</v>
+      </c>
+      <c r="B142" t="s">
         <v>423</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>424</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>425</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>426</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>427</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>428</v>
       </c>
-      <c r="G142" t="s">
+      <c r="H142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142" t="s">
         <v>429</v>
-      </c>
-      <c r="H142" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I142">
-        <v>1</v>
-      </c>
-      <c r="J142" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7710,10 +7710,10 @@
         <v>430</v>
       </c>
       <c r="B143" t="s">
+        <v>423</v>
+      </c>
+      <c r="C143" t="s">
         <v>424</v>
-      </c>
-      <c r="C143" t="s">
-        <v>425</v>
       </c>
       <c r="D143" t="s">
         <v>431</v>
@@ -7722,7 +7722,7 @@
         <v>432</v>
       </c>
       <c r="F143" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G143" t="s">
         <v>433</v>
@@ -7734,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7742,31 +7742,31 @@
         <v>434</v>
       </c>
       <c r="B144" t="s">
+        <v>423</v>
+      </c>
+      <c r="C144" t="s">
         <v>424</v>
-      </c>
-      <c r="C144" t="s">
-        <v>425</v>
       </c>
       <c r="D144" t="s">
         <v>435</v>
       </c>
       <c r="E144" t="s">
+        <v>426</v>
+      </c>
+      <c r="F144" t="s">
         <v>427</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>428</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144" t="s">
         <v>429</v>
-      </c>
-      <c r="H144" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I144">
-        <v>1</v>
-      </c>
-      <c r="J144" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7774,10 +7774,10 @@
         <v>436</v>
       </c>
       <c r="B145" t="s">
+        <v>423</v>
+      </c>
+      <c r="C145" t="s">
         <v>424</v>
-      </c>
-      <c r="C145" t="s">
-        <v>425</v>
       </c>
       <c r="D145" t="s">
         <v>437</v>
@@ -7786,7 +7786,7 @@
         <v>432</v>
       </c>
       <c r="F145" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G145" t="s">
         <v>433</v>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7806,31 +7806,31 @@
         <v>438</v>
       </c>
       <c r="B146" t="s">
+        <v>423</v>
+      </c>
+      <c r="C146" t="s">
         <v>424</v>
-      </c>
-      <c r="C146" t="s">
-        <v>425</v>
       </c>
       <c r="D146" t="s">
         <v>439</v>
       </c>
       <c r="E146" t="s">
+        <v>426</v>
+      </c>
+      <c r="F146" t="s">
         <v>427</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>428</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146" t="s">
         <v>429</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I146">
-        <v>1</v>
-      </c>
-      <c r="J146" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7838,10 +7838,10 @@
         <v>440</v>
       </c>
       <c r="B147" t="s">
+        <v>423</v>
+      </c>
+      <c r="C147" t="s">
         <v>424</v>
-      </c>
-      <c r="C147" t="s">
-        <v>425</v>
       </c>
       <c r="D147" t="s">
         <v>441</v>
@@ -7850,7 +7850,7 @@
         <v>432</v>
       </c>
       <c r="F147" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G147" t="s">
         <v>433</v>
@@ -7862,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7870,31 +7870,31 @@
         <v>442</v>
       </c>
       <c r="B148" t="s">
+        <v>423</v>
+      </c>
+      <c r="C148" t="s">
         <v>424</v>
-      </c>
-      <c r="C148" t="s">
-        <v>425</v>
       </c>
       <c r="D148" t="s">
         <v>443</v>
       </c>
       <c r="E148" t="s">
+        <v>426</v>
+      </c>
+      <c r="F148" t="s">
         <v>427</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>428</v>
       </c>
-      <c r="G148" t="s">
+      <c r="H148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148" t="s">
         <v>429</v>
-      </c>
-      <c r="H148" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I148">
-        <v>1</v>
-      </c>
-      <c r="J148" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -7902,10 +7902,10 @@
         <v>444</v>
       </c>
       <c r="B149" t="s">
+        <v>423</v>
+      </c>
+      <c r="C149" t="s">
         <v>424</v>
-      </c>
-      <c r="C149" t="s">
-        <v>425</v>
       </c>
       <c r="D149" t="s">
         <v>445</v>
@@ -7914,7 +7914,7 @@
         <v>432</v>
       </c>
       <c r="F149" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G149" t="s">
         <v>433</v>
@@ -7926,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -7934,31 +7934,31 @@
         <v>446</v>
       </c>
       <c r="B150" t="s">
+        <v>423</v>
+      </c>
+      <c r="C150" t="s">
         <v>424</v>
-      </c>
-      <c r="C150" t="s">
-        <v>425</v>
       </c>
       <c r="D150" t="s">
         <v>447</v>
       </c>
       <c r="E150" t="s">
+        <v>426</v>
+      </c>
+      <c r="F150" t="s">
         <v>427</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>428</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150" t="s">
         <v>429</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I150">
-        <v>1</v>
-      </c>
-      <c r="J150" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -7966,10 +7966,10 @@
         <v>448</v>
       </c>
       <c r="B151" t="s">
+        <v>423</v>
+      </c>
+      <c r="C151" t="s">
         <v>424</v>
-      </c>
-      <c r="C151" t="s">
-        <v>425</v>
       </c>
       <c r="D151" t="s">
         <v>449</v>
@@ -7978,7 +7978,7 @@
         <v>432</v>
       </c>
       <c r="F151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G151" t="s">
         <v>433</v>
@@ -7990,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -7998,31 +7998,31 @@
         <v>450</v>
       </c>
       <c r="B152" t="s">
+        <v>423</v>
+      </c>
+      <c r="C152" t="s">
         <v>424</v>
-      </c>
-      <c r="C152" t="s">
-        <v>425</v>
       </c>
       <c r="D152" t="s">
         <v>451</v>
       </c>
       <c r="E152" t="s">
+        <v>426</v>
+      </c>
+      <c r="F152" t="s">
         <v>427</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>428</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152" t="s">
         <v>429</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I152">
-        <v>1</v>
-      </c>
-      <c r="J152" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8030,10 +8030,10 @@
         <v>452</v>
       </c>
       <c r="B153" t="s">
+        <v>423</v>
+      </c>
+      <c r="C153" t="s">
         <v>424</v>
-      </c>
-      <c r="C153" t="s">
-        <v>425</v>
       </c>
       <c r="D153" t="s">
         <v>453</v>
@@ -8042,7 +8042,7 @@
         <v>432</v>
       </c>
       <c r="F153" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G153" t="s">
         <v>433</v>
@@ -8054,59 +8054,59 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>454</v>
+      </c>
+      <c r="B154" t="s">
+        <v>423</v>
+      </c>
+      <c r="C154" t="s">
+        <v>424</v>
+      </c>
+      <c r="D154" t="s">
         <v>455</v>
       </c>
-      <c r="B154" t="s">
-        <v>424</v>
-      </c>
-      <c r="C154" t="s">
-        <v>425</v>
-      </c>
-      <c r="D154" t="s">
-        <v>456</v>
-      </c>
       <c r="E154" t="s">
+        <v>426</v>
+      </c>
+      <c r="F154" t="s">
         <v>427</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>428</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154" t="s">
         <v>429</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I154">
-        <v>1</v>
-      </c>
-      <c r="J154" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>456</v>
+      </c>
+      <c r="B155" t="s">
+        <v>423</v>
+      </c>
+      <c r="C155" t="s">
+        <v>424</v>
+      </c>
+      <c r="D155" t="s">
         <v>457</v>
-      </c>
-      <c r="B155" t="s">
-        <v>424</v>
-      </c>
-      <c r="C155" t="s">
-        <v>425</v>
-      </c>
-      <c r="D155" t="s">
-        <v>458</v>
       </c>
       <c r="E155" t="s">
         <v>432</v>
       </c>
       <c r="F155" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G155" t="s">
         <v>433</v>
@@ -8118,59 +8118,59 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>458</v>
+      </c>
+      <c r="B156" t="s">
+        <v>423</v>
+      </c>
+      <c r="C156" t="s">
+        <v>424</v>
+      </c>
+      <c r="D156" t="s">
         <v>459</v>
       </c>
-      <c r="B156" t="s">
-        <v>424</v>
-      </c>
-      <c r="C156" t="s">
-        <v>425</v>
-      </c>
-      <c r="D156" t="s">
-        <v>460</v>
-      </c>
       <c r="E156" t="s">
+        <v>426</v>
+      </c>
+      <c r="F156" t="s">
         <v>427</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>428</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156" t="s">
         <v>429</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I156">
-        <v>1</v>
-      </c>
-      <c r="J156" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>460</v>
+      </c>
+      <c r="B157" t="s">
+        <v>423</v>
+      </c>
+      <c r="C157" t="s">
+        <v>424</v>
+      </c>
+      <c r="D157" t="s">
         <v>461</v>
-      </c>
-      <c r="B157" t="s">
-        <v>424</v>
-      </c>
-      <c r="C157" t="s">
-        <v>425</v>
-      </c>
-      <c r="D157" t="s">
-        <v>462</v>
       </c>
       <c r="E157" t="s">
         <v>432</v>
       </c>
       <c r="F157" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G157" t="s">
         <v>433</v>
@@ -8182,39 +8182,39 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>462</v>
+      </c>
+      <c r="B158" t="s">
+        <v>423</v>
+      </c>
+      <c r="C158" t="s">
+        <v>424</v>
+      </c>
+      <c r="D158" t="s">
         <v>463</v>
       </c>
-      <c r="B158" t="s">
-        <v>424</v>
-      </c>
-      <c r="C158" t="s">
-        <v>425</v>
-      </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>426</v>
+      </c>
+      <c r="F158" t="s">
+        <v>427</v>
+      </c>
+      <c r="G158" t="s">
+        <v>428</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158" t="s">
         <v>464</v>
-      </c>
-      <c r="E158" t="s">
-        <v>427</v>
-      </c>
-      <c r="F158" t="s">
-        <v>428</v>
-      </c>
-      <c r="G158" t="s">
-        <v>429</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I158">
-        <v>1</v>
-      </c>
-      <c r="J158" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -8222,10 +8222,10 @@
         <v>465</v>
       </c>
       <c r="B159" t="s">
+        <v>423</v>
+      </c>
+      <c r="C159" t="s">
         <v>424</v>
-      </c>
-      <c r="C159" t="s">
-        <v>425</v>
       </c>
       <c r="D159" t="s">
         <v>466</v>
@@ -8234,7 +8234,7 @@
         <v>432</v>
       </c>
       <c r="F159" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G159" t="s">
         <v>433</v>
@@ -8246,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -8254,23 +8254,23 @@
         <v>467</v>
       </c>
       <c r="B160" t="s">
+        <v>423</v>
+      </c>
+      <c r="C160" t="s">
         <v>424</v>
-      </c>
-      <c r="C160" t="s">
-        <v>425</v>
       </c>
       <c r="D160" t="s">
         <v>468</v>
       </c>
       <c r="E160" t="s">
+        <v>426</v>
+      </c>
+      <c r="F160" t="s">
         <v>427</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>428</v>
       </c>
-      <c r="G160" t="s">
-        <v>429</v>
-      </c>
       <c r="H160" s="3" t="s">
         <v>53</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -8286,10 +8286,10 @@
         <v>469</v>
       </c>
       <c r="B161" t="s">
+        <v>423</v>
+      </c>
+      <c r="C161" t="s">
         <v>424</v>
-      </c>
-      <c r="C161" t="s">
-        <v>425</v>
       </c>
       <c r="D161" t="s">
         <v>470</v>
@@ -8298,7 +8298,7 @@
         <v>432</v>
       </c>
       <c r="F161" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G161" t="s">
         <v>433</v>
@@ -8310,7 +8310,7 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -8318,23 +8318,23 @@
         <v>471</v>
       </c>
       <c r="B162" t="s">
+        <v>423</v>
+      </c>
+      <c r="C162" t="s">
         <v>424</v>
-      </c>
-      <c r="C162" t="s">
-        <v>425</v>
       </c>
       <c r="D162" t="s">
         <v>472</v>
       </c>
       <c r="E162" t="s">
+        <v>426</v>
+      </c>
+      <c r="F162" t="s">
         <v>427</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>428</v>
       </c>
-      <c r="G162" t="s">
-        <v>429</v>
-      </c>
       <c r="H162" s="3" t="s">
         <v>53</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -8350,10 +8350,10 @@
         <v>473</v>
       </c>
       <c r="B163" t="s">
+        <v>423</v>
+      </c>
+      <c r="C163" t="s">
         <v>424</v>
-      </c>
-      <c r="C163" t="s">
-        <v>425</v>
       </c>
       <c r="D163" t="s">
         <v>474</v>
@@ -8362,7 +8362,7 @@
         <v>432</v>
       </c>
       <c r="F163" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G163" t="s">
         <v>433</v>
@@ -8374,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -8382,23 +8382,23 @@
         <v>475</v>
       </c>
       <c r="B164" t="s">
+        <v>423</v>
+      </c>
+      <c r="C164" t="s">
         <v>424</v>
-      </c>
-      <c r="C164" t="s">
-        <v>425</v>
       </c>
       <c r="D164" t="s">
         <v>476</v>
       </c>
       <c r="E164" t="s">
+        <v>426</v>
+      </c>
+      <c r="F164" t="s">
         <v>427</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>428</v>
       </c>
-      <c r="G164" t="s">
-        <v>429</v>
-      </c>
       <c r="H164" s="3" t="s">
         <v>53</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -8414,10 +8414,10 @@
         <v>477</v>
       </c>
       <c r="B165" t="s">
+        <v>423</v>
+      </c>
+      <c r="C165" t="s">
         <v>424</v>
-      </c>
-      <c r="C165" t="s">
-        <v>425</v>
       </c>
       <c r="D165" t="s">
         <v>478</v>
@@ -8426,7 +8426,7 @@
         <v>432</v>
       </c>
       <c r="F165" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G165" t="s">
         <v>433</v>
@@ -8438,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -8446,23 +8446,23 @@
         <v>479</v>
       </c>
       <c r="B166" t="s">
+        <v>423</v>
+      </c>
+      <c r="C166" t="s">
         <v>424</v>
-      </c>
-      <c r="C166" t="s">
-        <v>425</v>
       </c>
       <c r="D166" t="s">
         <v>480</v>
       </c>
       <c r="E166" t="s">
+        <v>426</v>
+      </c>
+      <c r="F166" t="s">
         <v>427</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>428</v>
       </c>
-      <c r="G166" t="s">
-        <v>429</v>
-      </c>
       <c r="H166" s="3" t="s">
         <v>53</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -8478,10 +8478,10 @@
         <v>481</v>
       </c>
       <c r="B167" t="s">
+        <v>423</v>
+      </c>
+      <c r="C167" t="s">
         <v>424</v>
-      </c>
-      <c r="C167" t="s">
-        <v>425</v>
       </c>
       <c r="D167" t="s">
         <v>482</v>
@@ -8490,7 +8490,7 @@
         <v>432</v>
       </c>
       <c r="F167" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G167" t="s">
         <v>433</v>
@@ -8502,7 +8502,7 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -8510,23 +8510,23 @@
         <v>483</v>
       </c>
       <c r="B168" t="s">
+        <v>423</v>
+      </c>
+      <c r="C168" t="s">
         <v>424</v>
-      </c>
-      <c r="C168" t="s">
-        <v>425</v>
       </c>
       <c r="D168" t="s">
         <v>484</v>
       </c>
       <c r="E168" t="s">
+        <v>426</v>
+      </c>
+      <c r="F168" t="s">
         <v>427</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>428</v>
       </c>
-      <c r="G168" t="s">
-        <v>429</v>
-      </c>
       <c r="H168" s="3" t="s">
         <v>53</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -8542,10 +8542,10 @@
         <v>485</v>
       </c>
       <c r="B169" t="s">
+        <v>423</v>
+      </c>
+      <c r="C169" t="s">
         <v>424</v>
-      </c>
-      <c r="C169" t="s">
-        <v>425</v>
       </c>
       <c r="D169" t="s">
         <v>486</v>
@@ -8554,7 +8554,7 @@
         <v>432</v>
       </c>
       <c r="F169" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G169" t="s">
         <v>433</v>
@@ -8566,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -8574,23 +8574,23 @@
         <v>487</v>
       </c>
       <c r="B170" t="s">
+        <v>423</v>
+      </c>
+      <c r="C170" t="s">
         <v>424</v>
-      </c>
-      <c r="C170" t="s">
-        <v>425</v>
       </c>
       <c r="D170" t="s">
         <v>488</v>
       </c>
       <c r="E170" t="s">
+        <v>426</v>
+      </c>
+      <c r="F170" t="s">
         <v>427</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>428</v>
       </c>
-      <c r="G170" t="s">
-        <v>429</v>
-      </c>
       <c r="H170" s="3" t="s">
         <v>53</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -8606,10 +8606,10 @@
         <v>489</v>
       </c>
       <c r="B171" t="s">
+        <v>423</v>
+      </c>
+      <c r="C171" t="s">
         <v>424</v>
-      </c>
-      <c r="C171" t="s">
-        <v>425</v>
       </c>
       <c r="D171" t="s">
         <v>490</v>
@@ -8618,7 +8618,7 @@
         <v>432</v>
       </c>
       <c r="F171" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G171" t="s">
         <v>433</v>
@@ -8630,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8638,23 +8638,23 @@
         <v>491</v>
       </c>
       <c r="B172" t="s">
+        <v>423</v>
+      </c>
+      <c r="C172" t="s">
         <v>424</v>
-      </c>
-      <c r="C172" t="s">
-        <v>425</v>
       </c>
       <c r="D172" t="s">
         <v>492</v>
       </c>
       <c r="E172" t="s">
+        <v>426</v>
+      </c>
+      <c r="F172" t="s">
         <v>427</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>428</v>
       </c>
-      <c r="G172" t="s">
-        <v>429</v>
-      </c>
       <c r="H172" s="3" t="s">
         <v>53</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -8670,10 +8670,10 @@
         <v>493</v>
       </c>
       <c r="B173" t="s">
+        <v>423</v>
+      </c>
+      <c r="C173" t="s">
         <v>424</v>
-      </c>
-      <c r="C173" t="s">
-        <v>425</v>
       </c>
       <c r="D173" t="s">
         <v>494</v>
@@ -8682,7 +8682,7 @@
         <v>432</v>
       </c>
       <c r="F173" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G173" t="s">
         <v>433</v>
@@ -8694,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8702,23 +8702,23 @@
         <v>495</v>
       </c>
       <c r="B174" t="s">
+        <v>423</v>
+      </c>
+      <c r="C174" t="s">
         <v>424</v>
-      </c>
-      <c r="C174" t="s">
-        <v>425</v>
       </c>
       <c r="D174" t="s">
         <v>496</v>
       </c>
       <c r="E174" t="s">
+        <v>426</v>
+      </c>
+      <c r="F174" t="s">
         <v>427</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>428</v>
       </c>
-      <c r="G174" t="s">
-        <v>429</v>
-      </c>
       <c r="H174" s="3" t="s">
         <v>53</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -8734,10 +8734,10 @@
         <v>497</v>
       </c>
       <c r="B175" t="s">
+        <v>423</v>
+      </c>
+      <c r="C175" t="s">
         <v>424</v>
-      </c>
-      <c r="C175" t="s">
-        <v>425</v>
       </c>
       <c r="D175" t="s">
         <v>498</v>
@@ -8746,7 +8746,7 @@
         <v>432</v>
       </c>
       <c r="F175" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G175" t="s">
         <v>433</v>
@@ -8758,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8766,23 +8766,23 @@
         <v>499</v>
       </c>
       <c r="B176" t="s">
+        <v>423</v>
+      </c>
+      <c r="C176" t="s">
         <v>424</v>
-      </c>
-      <c r="C176" t="s">
-        <v>425</v>
       </c>
       <c r="D176" t="s">
         <v>500</v>
       </c>
       <c r="E176" t="s">
+        <v>426</v>
+      </c>
+      <c r="F176" t="s">
         <v>427</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>428</v>
       </c>
-      <c r="G176" t="s">
-        <v>429</v>
-      </c>
       <c r="H176" s="3" t="s">
         <v>53</v>
       </c>
@@ -8790,63 +8790,63 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>502</v>
+      </c>
+      <c r="B177" t="s">
+        <v>503</v>
+      </c>
+      <c r="C177" t="s">
+        <v>504</v>
+      </c>
+      <c r="D177" t="s">
+        <v>505</v>
+      </c>
+      <c r="E177" t="s">
+        <v>506</v>
+      </c>
+      <c r="F177" t="s">
+        <v>507</v>
+      </c>
+      <c r="G177" t="s">
+        <v>508</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177" t="s">
         <v>501</v>
-      </c>
-      <c r="B177" t="s">
-        <v>502</v>
-      </c>
-      <c r="C177" t="s">
-        <v>503</v>
-      </c>
-      <c r="D177" t="s">
-        <v>504</v>
-      </c>
-      <c r="E177" t="s">
-        <v>505</v>
-      </c>
-      <c r="F177" t="s">
-        <v>506</v>
-      </c>
-      <c r="G177" t="s">
-        <v>507</v>
-      </c>
-      <c r="H177" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I177">
-        <v>1</v>
-      </c>
-      <c r="J177" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>509</v>
+      </c>
+      <c r="B178" t="s">
+        <v>503</v>
+      </c>
+      <c r="C178" t="s">
+        <v>504</v>
+      </c>
+      <c r="D178" t="s">
+        <v>510</v>
+      </c>
+      <c r="E178" t="s">
+        <v>511</v>
+      </c>
+      <c r="F178" t="s">
+        <v>507</v>
+      </c>
+      <c r="G178" t="s">
         <v>508</v>
       </c>
-      <c r="B178" t="s">
-        <v>502</v>
-      </c>
-      <c r="C178" t="s">
-        <v>503</v>
-      </c>
-      <c r="D178" t="s">
-        <v>509</v>
-      </c>
-      <c r="E178" t="s">
-        <v>510</v>
-      </c>
-      <c r="F178" t="s">
-        <v>506</v>
-      </c>
-      <c r="G178" t="s">
-        <v>507</v>
-      </c>
       <c r="H178" s="3" t="s">
         <v>53</v>
       </c>
@@ -8854,30 +8854,30 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B179" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C179" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D179" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E179" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F179" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G179" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>53</v>
@@ -8886,30 +8886,30 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B180" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C180" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D180" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E180" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F180" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G180" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>53</v>
@@ -8918,30 +8918,30 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B181" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C181" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D181" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E181" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F181" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G181" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>53</v>
@@ -8950,30 +8950,30 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B182" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C182" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D182" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E182" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F182" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G182" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>53</v>
@@ -8982,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -8990,10 +8990,10 @@
         <v>524</v>
       </c>
       <c r="B183" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C183" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D183" t="s">
         <v>525</v>
@@ -9002,10 +9002,10 @@
         <v>526</v>
       </c>
       <c r="F183" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G183" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>53</v>
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -9022,10 +9022,10 @@
         <v>527</v>
       </c>
       <c r="B184" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C184" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D184" t="s">
         <v>528</v>
@@ -9034,10 +9034,10 @@
         <v>529</v>
       </c>
       <c r="F184" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G184" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H184" s="3" t="s">
         <v>53</v>
@@ -9046,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -9054,10 +9054,10 @@
         <v>530</v>
       </c>
       <c r="B185" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C185" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D185" t="s">
         <v>531</v>
@@ -9066,10 +9066,10 @@
         <v>532</v>
       </c>
       <c r="F185" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G185" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -9078,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -9086,10 +9086,10 @@
         <v>533</v>
       </c>
       <c r="B186" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C186" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D186" t="s">
         <v>534</v>
@@ -9098,10 +9098,10 @@
         <v>535</v>
       </c>
       <c r="F186" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G186" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -9110,7 +9110,7 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -9118,10 +9118,10 @@
         <v>536</v>
       </c>
       <c r="B187" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C187" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D187" t="s">
         <v>537</v>
@@ -9130,10 +9130,10 @@
         <v>538</v>
       </c>
       <c r="F187" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G187" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -9142,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -9150,10 +9150,10 @@
         <v>539</v>
       </c>
       <c r="B188" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C188" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D188" t="s">
         <v>540</v>
@@ -9162,10 +9162,10 @@
         <v>541</v>
       </c>
       <c r="F188" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G188" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -9174,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -9182,10 +9182,10 @@
         <v>542</v>
       </c>
       <c r="B189" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C189" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D189" t="s">
         <v>543</v>
@@ -9194,10 +9194,10 @@
         <v>544</v>
       </c>
       <c r="F189" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G189" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -9206,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -9214,10 +9214,10 @@
         <v>545</v>
       </c>
       <c r="B190" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C190" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D190" t="s">
         <v>546</v>
@@ -9226,10 +9226,10 @@
         <v>547</v>
       </c>
       <c r="F190" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G190" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -9238,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -9246,10 +9246,10 @@
         <v>548</v>
       </c>
       <c r="B191" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C191" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D191" t="s">
         <v>549</v>
@@ -9258,10 +9258,10 @@
         <v>550</v>
       </c>
       <c r="F191" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G191" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -9270,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -9278,10 +9278,10 @@
         <v>551</v>
       </c>
       <c r="B192" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C192" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D192" t="s">
         <v>552</v>
@@ -9290,10 +9290,10 @@
         <v>553</v>
       </c>
       <c r="F192" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G192" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -9302,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -9310,10 +9310,10 @@
         <v>554</v>
       </c>
       <c r="B193" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C193" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D193" t="s">
         <v>555</v>
@@ -9322,10 +9322,10 @@
         <v>556</v>
       </c>
       <c r="F193" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G193" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -9334,7 +9334,7 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -9342,10 +9342,10 @@
         <v>557</v>
       </c>
       <c r="B194" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C194" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D194" t="s">
         <v>558</v>
@@ -9354,10 +9354,10 @@
         <v>559</v>
       </c>
       <c r="F194" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G194" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -9366,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -9374,10 +9374,10 @@
         <v>560</v>
       </c>
       <c r="B195" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C195" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D195" t="s">
         <v>561</v>
@@ -9386,10 +9386,10 @@
         <v>562</v>
       </c>
       <c r="F195" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G195" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -9398,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -9406,10 +9406,10 @@
         <v>563</v>
       </c>
       <c r="B196" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C196" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D196" t="s">
         <v>564</v>
@@ -9418,10 +9418,10 @@
         <v>565</v>
       </c>
       <c r="F196" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G196" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -9430,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -9438,22 +9438,22 @@
         <v>566</v>
       </c>
       <c r="B197" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C197" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D197" t="s">
         <v>567</v>
       </c>
       <c r="E197" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F197" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G197" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -9462,7 +9462,7 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -9470,22 +9470,22 @@
         <v>568</v>
       </c>
       <c r="B198" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C198" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D198" t="s">
         <v>569</v>
       </c>
       <c r="E198" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F198" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G198" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -9494,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -9502,22 +9502,22 @@
         <v>570</v>
       </c>
       <c r="B199" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C199" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D199" t="s">
         <v>571</v>
       </c>
       <c r="E199" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F199" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G199" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -9526,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -9534,22 +9534,22 @@
         <v>572</v>
       </c>
       <c r="B200" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C200" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D200" t="s">
         <v>573</v>
       </c>
       <c r="E200" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F200" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G200" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -9558,7 +9558,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -9566,22 +9566,22 @@
         <v>574</v>
       </c>
       <c r="B201" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C201" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D201" t="s">
         <v>575</v>
       </c>
       <c r="E201" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F201" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G201" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -9590,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -9598,22 +9598,22 @@
         <v>576</v>
       </c>
       <c r="B202" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C202" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D202" t="s">
         <v>577</v>
       </c>
       <c r="E202" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F202" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G202" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -9622,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -9630,10 +9630,10 @@
         <v>578</v>
       </c>
       <c r="B203" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C203" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D203" t="s">
         <v>579</v>
@@ -9642,10 +9642,10 @@
         <v>526</v>
       </c>
       <c r="F203" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G203" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -9654,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -9662,10 +9662,10 @@
         <v>580</v>
       </c>
       <c r="B204" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C204" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D204" t="s">
         <v>581</v>
@@ -9674,10 +9674,10 @@
         <v>529</v>
       </c>
       <c r="F204" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G204" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -9686,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -9694,10 +9694,10 @@
         <v>582</v>
       </c>
       <c r="B205" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C205" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D205" t="s">
         <v>583</v>
@@ -9706,10 +9706,10 @@
         <v>532</v>
       </c>
       <c r="F205" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G205" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -9718,30 +9718,30 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B206" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C206" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D206" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E206" t="s">
         <v>535</v>
       </c>
       <c r="F206" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G206" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -9750,30 +9750,30 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B207" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C207" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D207" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E207" t="s">
         <v>538</v>
       </c>
       <c r="F207" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G207" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -9782,30 +9782,30 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B208" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C208" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D208" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E208" t="s">
         <v>541</v>
       </c>
       <c r="F208" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G208" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -9814,30 +9814,30 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B209" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C209" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D209" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E209" t="s">
         <v>544</v>
       </c>
       <c r="F209" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G209" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -9846,30 +9846,30 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B210" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C210" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D210" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E210" t="s">
         <v>547</v>
       </c>
       <c r="F210" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G210" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -9878,30 +9878,30 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B211" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C211" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D211" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E211" t="s">
         <v>550</v>
       </c>
       <c r="F211" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G211" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -9910,7 +9910,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9942,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -9974,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -10006,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -10038,7 +10038,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -10070,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -10102,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -10134,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -10166,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -10198,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -10230,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -10262,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -10294,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -10326,7 +10326,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -10358,7 +10358,7 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -10390,7 +10390,7 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -10422,7 +10422,7 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -10454,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -10486,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -10518,7 +10518,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -10550,7 +10550,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -10582,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -10614,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -10646,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -10678,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -10710,7 +10710,7 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -10742,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -10774,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -10806,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -10838,7 +10838,7 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -10902,7 +10902,7 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -10934,12 +10934,12 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B244" t="s">
         <v>692</v>
@@ -10948,10 +10948,10 @@
         <v>693</v>
       </c>
       <c r="D244" t="s">
+        <v>702</v>
+      </c>
+      <c r="E244" t="s">
         <v>703</v>
-      </c>
-      <c r="E244" t="s">
-        <v>704</v>
       </c>
       <c r="F244" t="s">
         <v>696</v>
@@ -10966,12 +10966,12 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B245" t="s">
         <v>692</v>
@@ -10980,17 +10980,17 @@
         <v>693</v>
       </c>
       <c r="D245" t="s">
+        <v>705</v>
+      </c>
+      <c r="E245" t="s">
         <v>706</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>707</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>708</v>
       </c>
-      <c r="G245" t="s">
-        <v>709</v>
-      </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
       </c>
@@ -10998,12 +10998,12 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B246" t="s">
         <v>692</v>
@@ -11012,17 +11012,17 @@
         <v>693</v>
       </c>
       <c r="D246" t="s">
+        <v>710</v>
+      </c>
+      <c r="E246" t="s">
         <v>711</v>
       </c>
-      <c r="E246" t="s">
-        <v>712</v>
-      </c>
       <c r="F246" t="s">
+        <v>707</v>
+      </c>
+      <c r="G246" t="s">
         <v>708</v>
       </c>
-      <c r="G246" t="s">
-        <v>709</v>
-      </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
       </c>
@@ -11030,12 +11030,12 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B247" t="s">
         <v>692</v>
@@ -11044,10 +11044,10 @@
         <v>693</v>
       </c>
       <c r="D247" t="s">
+        <v>713</v>
+      </c>
+      <c r="E247" t="s">
         <v>714</v>
-      </c>
-      <c r="E247" t="s">
-        <v>715</v>
       </c>
       <c r="F247" t="s">
         <v>696</v>
@@ -11062,12 +11062,12 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B248" t="s">
         <v>692</v>
@@ -11076,10 +11076,10 @@
         <v>693</v>
       </c>
       <c r="D248" t="s">
+        <v>716</v>
+      </c>
+      <c r="E248" t="s">
         <v>717</v>
-      </c>
-      <c r="E248" t="s">
-        <v>718</v>
       </c>
       <c r="F248" t="s">
         <v>696</v>
@@ -11094,12 +11094,12 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B249" t="s">
         <v>692</v>
@@ -11108,10 +11108,10 @@
         <v>693</v>
       </c>
       <c r="D249" t="s">
+        <v>719</v>
+      </c>
+      <c r="E249" t="s">
         <v>720</v>
-      </c>
-      <c r="E249" t="s">
-        <v>721</v>
       </c>
       <c r="F249" t="s">
         <v>696</v>
@@ -11126,12 +11126,12 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B250" t="s">
         <v>692</v>
@@ -11140,17 +11140,17 @@
         <v>693</v>
       </c>
       <c r="D250" t="s">
+        <v>722</v>
+      </c>
+      <c r="E250" t="s">
         <v>723</v>
       </c>
-      <c r="E250" t="s">
-        <v>724</v>
-      </c>
       <c r="F250" t="s">
+        <v>707</v>
+      </c>
+      <c r="G250" t="s">
         <v>708</v>
       </c>
-      <c r="G250" t="s">
-        <v>709</v>
-      </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
       </c>
@@ -11158,12 +11158,12 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B251" t="s">
         <v>692</v>
@@ -11172,17 +11172,17 @@
         <v>693</v>
       </c>
       <c r="D251" t="s">
+        <v>725</v>
+      </c>
+      <c r="E251" t="s">
         <v>726</v>
       </c>
-      <c r="E251" t="s">
-        <v>727</v>
-      </c>
       <c r="F251" t="s">
+        <v>707</v>
+      </c>
+      <c r="G251" t="s">
         <v>708</v>
       </c>
-      <c r="G251" t="s">
-        <v>709</v>
-      </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
       </c>
@@ -11190,12 +11190,12 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B252" t="s">
         <v>692</v>
@@ -11204,7 +11204,7 @@
         <v>693</v>
       </c>
       <c r="D252" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E252" t="s">
         <v>695</v>
@@ -11222,12 +11222,12 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B253" t="s">
         <v>692</v>
@@ -11236,7 +11236,7 @@
         <v>693</v>
       </c>
       <c r="D253" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E253" t="s">
         <v>700</v>
@@ -11254,12 +11254,12 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B254" t="s">
         <v>692</v>
@@ -11268,10 +11268,10 @@
         <v>693</v>
       </c>
       <c r="D254" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E254" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F254" t="s">
         <v>696</v>
@@ -11286,12 +11286,12 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B255" t="s">
         <v>692</v>
@@ -11300,17 +11300,17 @@
         <v>693</v>
       </c>
       <c r="D255" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E255" t="s">
+        <v>706</v>
+      </c>
+      <c r="F255" t="s">
         <v>707</v>
       </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
         <v>708</v>
       </c>
-      <c r="G255" t="s">
-        <v>709</v>
-      </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
       </c>
@@ -11318,12 +11318,12 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B256" t="s">
         <v>692</v>
@@ -11332,17 +11332,17 @@
         <v>693</v>
       </c>
       <c r="D256" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E256" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F256" t="s">
+        <v>707</v>
+      </c>
+      <c r="G256" t="s">
         <v>708</v>
       </c>
-      <c r="G256" t="s">
-        <v>709</v>
-      </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
       </c>
@@ -11350,12 +11350,12 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B257" t="s">
         <v>692</v>
@@ -11364,10 +11364,10 @@
         <v>693</v>
       </c>
       <c r="D257" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E257" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F257" t="s">
         <v>696</v>
@@ -11382,12 +11382,12 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B258" t="s">
         <v>692</v>
@@ -11396,10 +11396,10 @@
         <v>693</v>
       </c>
       <c r="D258" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E258" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F258" t="s">
         <v>696</v>
@@ -11414,12 +11414,12 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B259" t="s">
         <v>692</v>
@@ -11428,10 +11428,10 @@
         <v>693</v>
       </c>
       <c r="D259" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E259" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F259" t="s">
         <v>696</v>
@@ -11446,12 +11446,12 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B260" t="s">
         <v>692</v>
@@ -11460,17 +11460,17 @@
         <v>693</v>
       </c>
       <c r="D260" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E260" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F260" t="s">
+        <v>707</v>
+      </c>
+      <c r="G260" t="s">
         <v>708</v>
       </c>
-      <c r="G260" t="s">
-        <v>709</v>
-      </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
       </c>
@@ -11478,12 +11478,12 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B261" t="s">
         <v>692</v>
@@ -11492,17 +11492,17 @@
         <v>693</v>
       </c>
       <c r="D261" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E261" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F261" t="s">
+        <v>707</v>
+      </c>
+      <c r="G261" t="s">
         <v>708</v>
       </c>
-      <c r="G261" t="s">
-        <v>709</v>
-      </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
       </c>
@@ -11510,12 +11510,12 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B262" t="s">
         <v>692</v>
@@ -11524,7 +11524,7 @@
         <v>693</v>
       </c>
       <c r="D262" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E262" t="s">
         <v>695</v>
@@ -11542,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -11574,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
@@ -11591,7 +11591,7 @@
         <v>753</v>
       </c>
       <c r="E264" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F264" t="s">
         <v>696</v>
@@ -11606,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -11623,14 +11623,14 @@
         <v>755</v>
       </c>
       <c r="E265" t="s">
+        <v>706</v>
+      </c>
+      <c r="F265" t="s">
         <v>707</v>
       </c>
-      <c r="F265" t="s">
+      <c r="G265" t="s">
         <v>708</v>
       </c>
-      <c r="G265" t="s">
-        <v>709</v>
-      </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
@@ -11655,14 +11655,14 @@
         <v>757</v>
       </c>
       <c r="E266" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F266" t="s">
+        <v>707</v>
+      </c>
+      <c r="G266" t="s">
         <v>708</v>
       </c>
-      <c r="G266" t="s">
-        <v>709</v>
-      </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -11687,7 +11687,7 @@
         <v>759</v>
       </c>
       <c r="E267" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F267" t="s">
         <v>696</v>
@@ -11702,7 +11702,7 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
@@ -11719,7 +11719,7 @@
         <v>761</v>
       </c>
       <c r="E268" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F268" t="s">
         <v>696</v>
@@ -11734,7 +11734,7 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -11751,7 +11751,7 @@
         <v>763</v>
       </c>
       <c r="E269" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F269" t="s">
         <v>696</v>
@@ -11766,7 +11766,7 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -11783,14 +11783,14 @@
         <v>765</v>
       </c>
       <c r="E270" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F270" t="s">
+        <v>707</v>
+      </c>
+      <c r="G270" t="s">
         <v>708</v>
       </c>
-      <c r="G270" t="s">
-        <v>709</v>
-      </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -11815,14 +11815,14 @@
         <v>767</v>
       </c>
       <c r="E271" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F271" t="s">
+        <v>707</v>
+      </c>
+      <c r="G271" t="s">
         <v>708</v>
       </c>
-      <c r="G271" t="s">
-        <v>709</v>
-      </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -11862,7 +11862,7 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -11894,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -11926,7 +11926,7 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -11958,7 +11958,7 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
@@ -11990,7 +11990,7 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
@@ -12022,7 +12022,7 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
@@ -12054,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
@@ -12086,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
@@ -12118,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
@@ -12150,7 +12150,7 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
@@ -12182,7 +12182,7 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -12214,7 +12214,7 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -12246,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -12278,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -12310,7 +12310,7 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
@@ -12342,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -12374,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -12406,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -12438,7 +12438,7 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -12470,7 +12470,7 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -12502,7 +12502,7 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -12534,7 +12534,7 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -12566,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -12598,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -12630,7 +12630,7 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -12662,7 +12662,7 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -12694,7 +12694,7 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -12726,7 +12726,7 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -12758,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -12790,7 +12790,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>
